--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B603E3-97C4-4AB2-80F8-FA477C24C95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D5C6AF-FB36-43C7-98AC-DF30C96BC3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="7" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D5C6AF-FB36-43C7-98AC-DF30C96BC3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8D07A7-4EBB-4F7F-8BBE-DA7BE2642DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11054" uniqueCount="2052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11092" uniqueCount="2056">
   <si>
     <t>NAME</t>
   </si>
@@ -6340,6 +6340,18 @@
   </si>
   <si>
     <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1#shield,1#armor,1#sword,1,4,4#heal_potion,5#mana_potion,5#cure_potion,3#wood,100#adorn_atk,1,1,3#adorn_hp,1#adorn_magic,1#twilight_fang,1#whispering_locket,1#ashen_knight_bulwark,1#ashen_knight_helm,1#ashen_knight_greaves,1#ashen_knight_pendant,1#ashen_knight_signet,1#ashen_knight_plate,1#adorn_crit,1#adorn_critdmg,1</t>
+  </si>
+  <si>
+    <t>basic_guts</t>
+  </si>
+  <si>
+    <t>buff_guts1</t>
+  </si>
+  <si>
+    <t>buff_guts1,100</t>
+  </si>
+  <si>
+    <t>guts,1</t>
   </si>
 </sst>
 </file>
@@ -44020,7 +44032,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
@@ -45157,35 +45169,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
-      <c r="A72" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>36</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
+      </c>
+      <c r="C71">
         <v>100</v>
       </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72" t="s">
-        <v>1854</v>
-      </c>
-      <c r="G72">
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>2052</v>
+      </c>
+      <c r="G71">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>36</v>
+        <v>1999</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73">
         <v>100</v>
@@ -45197,7 +45209,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -45208,7 +45220,7 @@
         <v>36</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
         <v>100</v>
@@ -45220,9 +45232,32 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>36</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>100</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75" t="s">
         <v>1846</v>
       </c>
-      <c r="G74">
+      <c r="G75">
         <v>0</v>
       </c>
     </row>
@@ -64744,7 +64779,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:BL107"/>
+  <dimension ref="A1:BL109"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
@@ -74741,7 +74776,7 @@
     </row>
     <row r="53" spans="1:63">
       <c r="A53" s="44" t="s">
-        <v>1797</v>
+        <v>2052</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -74840,7 +74875,7 @@
         <v>36</v>
       </c>
       <c r="AH53" t="s">
-        <v>1919</v>
+        <v>2054</v>
       </c>
       <c r="AI53" s="44" t="s">
         <v>1479</v>
@@ -74932,7 +74967,7 @@
     </row>
     <row r="54" spans="1:63">
       <c r="A54" s="44" t="s">
-        <v>1796</v>
+        <v>2053</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -74944,7 +74979,7 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -75115,7 +75150,7 @@
         <v>0</v>
       </c>
       <c r="BJ54" s="46" t="s">
-        <v>36</v>
+        <v>2055</v>
       </c>
       <c r="BK54" t="s">
         <v>36</v>
@@ -75123,7 +75158,7 @@
     </row>
     <row r="55" spans="1:63">
       <c r="A55" s="44" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -75180,7 +75215,7 @@
         <v>0</v>
       </c>
       <c r="T55">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U55">
         <v>0</v>
@@ -75192,7 +75227,7 @@
         <v>3</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y55">
         <v>0</v>
@@ -75222,13 +75257,13 @@
         <v>36</v>
       </c>
       <c r="AH55" t="s">
-        <v>36</v>
+        <v>1919</v>
       </c>
       <c r="AI55" s="44" t="s">
         <v>1479</v>
       </c>
       <c r="AJ55" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK55" s="44" t="s">
         <v>1470</v>
@@ -75294,7 +75329,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="BG55" t="s">
         <v>36</v>
@@ -75314,10 +75349,10 @@
     </row>
     <row r="56" spans="1:63">
       <c r="A56" s="44" t="s">
-        <v>1807</v>
+        <v>1796</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -75326,7 +75361,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -75401,13 +75436,13 @@
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE56">
         <v>0</v>
       </c>
       <c r="AF56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="s">
         <v>36</v>
@@ -75419,7 +75454,7 @@
         <v>1479</v>
       </c>
       <c r="AJ56" s="44" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="AK56" s="44" t="s">
         <v>1470</v>
@@ -75443,7 +75478,7 @@
         <v>0</v>
       </c>
       <c r="AR56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS56">
         <v>1</v>
@@ -75461,7 +75496,7 @@
         <v>0</v>
       </c>
       <c r="AX56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY56" t="s">
         <v>36</v>
@@ -75485,13 +75520,13 @@
         <v>0</v>
       </c>
       <c r="BF56" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG56" t="s">
         <v>36</v>
       </c>
       <c r="BH56" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI56">
         <v>0</v>
@@ -75505,7 +75540,7 @@
     </row>
     <row r="57" spans="1:63">
       <c r="A57" s="44" t="s">
-        <v>1934</v>
+        <v>1805</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -75517,52 +75552,52 @@
         <v>0</v>
       </c>
       <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
         <v>50</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <v>0</v>
       </c>
       <c r="U57">
         <v>0</v>
@@ -75574,7 +75609,7 @@
         <v>3</v>
       </c>
       <c r="X57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y57">
         <v>0</v>
@@ -75604,13 +75639,13 @@
         <v>36</v>
       </c>
       <c r="AH57" t="s">
-        <v>1936</v>
+        <v>36</v>
       </c>
       <c r="AI57" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ57" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK57" s="44" t="s">
         <v>1470</v>
@@ -75676,13 +75711,13 @@
         <v>0</v>
       </c>
       <c r="BF57" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="BG57" t="s">
         <v>36</v>
       </c>
       <c r="BH57" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI57">
         <v>0</v>
@@ -75696,7 +75731,7 @@
     </row>
     <row r="58" spans="1:63">
       <c r="A58" s="44" t="s">
-        <v>1935</v>
+        <v>1807</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -75783,13 +75818,13 @@
         <v>0</v>
       </c>
       <c r="AD58">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AE58">
         <v>0</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG58" t="s">
         <v>36</v>
@@ -75798,10 +75833,10 @@
         <v>36</v>
       </c>
       <c r="AI58" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ58" s="44" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="AK58" s="44" t="s">
         <v>1470</v>
@@ -75825,7 +75860,7 @@
         <v>0</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS58">
         <v>1</v>
@@ -75843,7 +75878,7 @@
         <v>0</v>
       </c>
       <c r="AX58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY58" t="s">
         <v>36</v>
@@ -75867,19 +75902,19 @@
         <v>0</v>
       </c>
       <c r="BF58" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG58" t="s">
         <v>36</v>
       </c>
       <c r="BH58" t="s">
-        <v>896</v>
+        <v>1671</v>
       </c>
       <c r="BI58">
         <v>0</v>
       </c>
       <c r="BJ58" s="46" t="s">
-        <v>1937</v>
+        <v>36</v>
       </c>
       <c r="BK58" t="s">
         <v>36</v>
@@ -75887,7 +75922,7 @@
     </row>
     <row r="59" spans="1:63">
       <c r="A59" s="44" t="s">
-        <v>1868</v>
+        <v>1934</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -75986,7 +76021,7 @@
         <v>36</v>
       </c>
       <c r="AH59" t="s">
-        <v>1920</v>
+        <v>1936</v>
       </c>
       <c r="AI59" s="44" t="s">
         <v>1363</v>
@@ -76058,7 +76093,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="BG59" t="s">
         <v>36</v>
@@ -76078,16 +76113,16 @@
     </row>
     <row r="60" spans="1:63">
       <c r="A60" s="44" t="s">
-        <v>1869</v>
+        <v>1935</v>
       </c>
       <c r="B60">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -76261,7 +76296,7 @@
         <v>0</v>
       </c>
       <c r="BJ60" s="46" t="s">
-        <v>36</v>
+        <v>1937</v>
       </c>
       <c r="BK60" t="s">
         <v>36</v>
@@ -76269,7 +76304,7 @@
     </row>
     <row r="61" spans="1:63">
       <c r="A61" s="44" t="s">
-        <v>1925</v>
+        <v>1868</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -76281,7 +76316,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -76368,10 +76403,10 @@
         <v>36</v>
       </c>
       <c r="AH61" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AI61" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ61" s="44" t="s">
         <v>1470</v>
@@ -76446,7 +76481,7 @@
         <v>36</v>
       </c>
       <c r="BH61" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="BI61">
         <v>0</v>
@@ -76460,16 +76495,16 @@
     </row>
     <row r="62" spans="1:63">
       <c r="A62" s="44" t="s">
-        <v>1926</v>
+        <v>1869</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -76490,7 +76525,7 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -76562,7 +76597,7 @@
         <v>36</v>
       </c>
       <c r="AI62" s="44" t="s">
-        <v>1479</v>
+        <v>1363</v>
       </c>
       <c r="AJ62" s="44" t="s">
         <v>1470</v>
@@ -76637,7 +76672,7 @@
         <v>36</v>
       </c>
       <c r="BH62" t="s">
-        <v>1663</v>
+        <v>896</v>
       </c>
       <c r="BI62">
         <v>0</v>
@@ -76651,7 +76686,7 @@
     </row>
     <row r="63" spans="1:63">
       <c r="A63" s="44" t="s">
-        <v>1870</v>
+        <v>1925</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -76842,7 +76877,7 @@
     </row>
     <row r="64" spans="1:63">
       <c r="A64" s="44" t="s">
-        <v>1871</v>
+        <v>1926</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -76869,10 +76904,10 @@
         <v>0</v>
       </c>
       <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
         <v>50</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -77033,7 +77068,7 @@
     </row>
     <row r="65" spans="1:63">
       <c r="A65" s="44" t="s">
-        <v>1882</v>
+        <v>1870</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -77051,7 +77086,7 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -77099,10 +77134,10 @@
         <v>0</v>
       </c>
       <c r="W65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y65">
         <v>0</v>
@@ -77132,10 +77167,10 @@
         <v>36</v>
       </c>
       <c r="AH65" t="s">
-        <v>36</v>
+        <v>1921</v>
       </c>
       <c r="AI65" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ65" s="44" t="s">
         <v>1470</v>
@@ -77204,7 +77239,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="s">
-        <v>37</v>
+        <v>1763</v>
       </c>
       <c r="BG65" t="s">
         <v>36</v>
@@ -77224,10 +77259,10 @@
     </row>
     <row r="66" spans="1:63">
       <c r="A66" s="44" t="s">
-        <v>1883</v>
+        <v>1871</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -77242,7 +77277,7 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -77251,7 +77286,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -77290,7 +77325,7 @@
         <v>0</v>
       </c>
       <c r="W66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X66">
         <v>0</v>
@@ -77311,13 +77346,13 @@
         <v>0</v>
       </c>
       <c r="AD66">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE66">
         <v>0</v>
       </c>
       <c r="AF66">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="s">
         <v>36</v>
@@ -77326,7 +77361,7 @@
         <v>36</v>
       </c>
       <c r="AI66" s="44" t="s">
-        <v>1363</v>
+        <v>1479</v>
       </c>
       <c r="AJ66" s="44" t="s">
         <v>1470</v>
@@ -77353,7 +77388,7 @@
         <v>0</v>
       </c>
       <c r="AR66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS66">
         <v>1</v>
@@ -77371,7 +77406,7 @@
         <v>0</v>
       </c>
       <c r="AX66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY66" t="s">
         <v>36</v>
@@ -77395,7 +77430,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="BG66" t="s">
         <v>36</v>
@@ -77415,7 +77450,7 @@
     </row>
     <row r="67" spans="1:63">
       <c r="A67" s="44" t="s">
-        <v>1908</v>
+        <v>1882</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -77586,7 +77621,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="s">
-        <v>1763</v>
+        <v>37</v>
       </c>
       <c r="BG67" t="s">
         <v>36</v>
@@ -77606,7 +77641,7 @@
     </row>
     <row r="68" spans="1:63">
       <c r="A68" s="44" t="s">
-        <v>1907</v>
+        <v>1883</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -77777,7 +77812,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="BG68" t="s">
         <v>36</v>
@@ -77797,7 +77832,7 @@
     </row>
     <row r="69" spans="1:63">
       <c r="A69" s="44" t="s">
-        <v>1884</v>
+        <v>1908</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -77968,7 +78003,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="BG69" t="s">
         <v>36</v>
@@ -77988,7 +78023,7 @@
     </row>
     <row r="70" spans="1:63">
       <c r="A70" s="44" t="s">
-        <v>1938</v>
+        <v>1907</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -78006,7 +78041,7 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -78084,10 +78119,10 @@
         <v>10</v>
       </c>
       <c r="AG70" t="s">
-        <v>1941</v>
+        <v>36</v>
       </c>
       <c r="AH70" t="s">
-        <v>1939</v>
+        <v>36</v>
       </c>
       <c r="AI70" s="44" t="s">
         <v>1363</v>
@@ -78159,7 +78194,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="BG70" t="s">
         <v>36</v>
@@ -78179,100 +78214,100 @@
     </row>
     <row r="71" spans="1:63">
       <c r="A71" s="44" t="s">
-        <v>1940</v>
+        <v>1884</v>
       </c>
       <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>4</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>1</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
         <v>-1</v>
       </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71">
-        <v>50</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>3</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>0</v>
-      </c>
-      <c r="AB71">
-        <v>1</v>
-      </c>
-      <c r="AC71">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>5</v>
-      </c>
       <c r="AE71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG71" t="s">
         <v>36</v>
@@ -78299,7 +78334,7 @@
         <v>1</v>
       </c>
       <c r="AO71" s="44" t="s">
-        <v>1407</v>
+        <v>36</v>
       </c>
       <c r="AP71" s="44">
         <v>0</v>
@@ -78326,7 +78361,7 @@
         <v>0</v>
       </c>
       <c r="AX71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY71" t="s">
         <v>36</v>
@@ -78350,13 +78385,13 @@
         <v>0</v>
       </c>
       <c r="BF71" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="BG71" t="s">
         <v>36</v>
       </c>
       <c r="BH71" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="BI71">
         <v>0</v>
@@ -78368,45 +78403,203 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:63" ht="14">
-      <c r="A72" s="55" t="s">
-        <v>1886</v>
-      </c>
-      <c r="B72" s="55"/>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="G72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="3"/>
-      <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
+    <row r="72" spans="1:63">
+      <c r="A72" s="44" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>4</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>1</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>-1</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>10</v>
+      </c>
       <c r="AG72" t="s">
-        <v>36</v>
+        <v>1941</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>1939</v>
+      </c>
+      <c r="AI72" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ72" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK72" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL72" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN72" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO72" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP72" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>1</v>
+      </c>
+      <c r="AS72">
+        <v>1</v>
+      </c>
+      <c r="AT72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU72">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW72">
+        <v>0</v>
+      </c>
+      <c r="AX72">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB72">
+        <v>0</v>
+      </c>
+      <c r="BC72">
+        <v>0</v>
+      </c>
+      <c r="BD72">
+        <v>0</v>
+      </c>
+      <c r="BE72">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG72" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH72" t="s">
+        <v>1663</v>
       </c>
       <c r="BI72">
         <v>0</v>
       </c>
       <c r="BJ72" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="BK72" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:63">
       <c r="A73" s="44" t="s">
-        <v>1887</v>
+        <v>1940</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -78415,7 +78608,7 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -78424,10 +78617,10 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -78490,13 +78683,13 @@
         <v>0</v>
       </c>
       <c r="AD73">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF73">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="s">
         <v>36</v>
@@ -78523,7 +78716,7 @@
         <v>1</v>
       </c>
       <c r="AO73" s="44" t="s">
-        <v>36</v>
+        <v>1407</v>
       </c>
       <c r="AP73" s="44">
         <v>0</v>
@@ -78532,7 +78725,7 @@
         <v>0</v>
       </c>
       <c r="AR73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS73">
         <v>1</v>
@@ -78550,7 +78743,7 @@
         <v>0</v>
       </c>
       <c r="AX73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY73" t="s">
         <v>36</v>
@@ -78571,19 +78764,19 @@
         <v>0</v>
       </c>
       <c r="BE73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF73" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="BG73" t="s">
         <v>36</v>
       </c>
       <c r="BH73" t="s">
-        <v>1659</v>
+        <v>1671</v>
       </c>
       <c r="BI73">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BJ73" s="46" t="s">
         <v>36</v>
@@ -78592,200 +78785,42 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:63">
-      <c r="A74" s="44" t="s">
-        <v>1888</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>10</v>
-      </c>
-      <c r="Q74">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>0</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>0</v>
-      </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
-      <c r="W74">
-        <v>3</v>
-      </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <v>0</v>
-      </c>
-      <c r="Z74">
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <v>0</v>
-      </c>
-      <c r="AB74">
-        <v>1</v>
-      </c>
-      <c r="AC74">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>-1</v>
-      </c>
-      <c r="AE74">
-        <v>0</v>
-      </c>
-      <c r="AF74">
-        <v>10</v>
-      </c>
+    <row r="74" spans="1:63" ht="14">
+      <c r="A74" s="55" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B74" s="55"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="55"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
       <c r="AG74" t="s">
         <v>36</v>
       </c>
-      <c r="AH74" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI74" s="44" t="s">
-        <v>1363</v>
-      </c>
-      <c r="AJ74" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AK74" s="44" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AL74" s="44">
-        <v>0</v>
-      </c>
-      <c r="AM74" s="44" t="s">
-        <v>1474</v>
-      </c>
-      <c r="AN74" s="44">
-        <v>1</v>
-      </c>
-      <c r="AO74" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP74" s="44">
-        <v>0</v>
-      </c>
-      <c r="AQ74">
-        <v>0</v>
-      </c>
-      <c r="AR74">
-        <v>0</v>
-      </c>
-      <c r="AS74">
-        <v>1</v>
-      </c>
-      <c r="AT74" t="s">
-        <v>36</v>
-      </c>
-      <c r="AU74">
-        <v>0</v>
-      </c>
-      <c r="AV74" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW74">
-        <v>0</v>
-      </c>
-      <c r="AX74">
-        <v>0</v>
-      </c>
-      <c r="AY74" t="s">
-        <v>36</v>
-      </c>
-      <c r="AZ74" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA74" t="s">
-        <v>36</v>
-      </c>
-      <c r="BB74">
-        <v>0</v>
-      </c>
-      <c r="BC74">
-        <v>0</v>
-      </c>
-      <c r="BD74">
-        <v>0</v>
-      </c>
-      <c r="BE74">
-        <v>1</v>
-      </c>
-      <c r="BF74" t="s">
-        <v>1762</v>
-      </c>
-      <c r="BG74" t="s">
-        <v>36</v>
-      </c>
-      <c r="BH74" t="s">
-        <v>1659</v>
-      </c>
       <c r="BI74">
         <v>0</v>
       </c>
       <c r="BJ74" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="BK74" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:63">
       <c r="A75" s="44" t="s">
-        <v>1897</v>
+        <v>1887</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -78806,10 +78841,10 @@
         <v>0</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -78965,10 +79000,10 @@
         <v>1659</v>
       </c>
       <c r="BI75">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BJ75" s="46" t="s">
-        <v>1900</v>
+        <v>36</v>
       </c>
       <c r="BK75" t="s">
         <v>36</v>
@@ -78976,7 +79011,7 @@
     </row>
     <row r="76" spans="1:63">
       <c r="A76" s="44" t="s">
-        <v>1901</v>
+        <v>1888</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -79021,7 +79056,7 @@
         <v>0</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -79159,7 +79194,7 @@
         <v>0</v>
       </c>
       <c r="BJ76" s="46" t="s">
-        <v>1902</v>
+        <v>36</v>
       </c>
       <c r="BK76" t="s">
         <v>36</v>
@@ -79167,7 +79202,7 @@
     </row>
     <row r="77" spans="1:63">
       <c r="A77" s="44" t="s">
-        <v>1943</v>
+        <v>1897</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -79350,56 +79385,393 @@
         <v>0</v>
       </c>
       <c r="BJ77" s="46" t="s">
+        <v>1900</v>
+      </c>
+      <c r="BK77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:63">
+      <c r="A78" s="44" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>3</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>1</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78">
+        <v>-1</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>10</v>
+      </c>
+      <c r="AG78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI78" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ78" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK78" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL78" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN78" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO78" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP78" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ78">
+        <v>0</v>
+      </c>
+      <c r="AR78">
+        <v>0</v>
+      </c>
+      <c r="AS78">
+        <v>1</v>
+      </c>
+      <c r="AT78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU78">
+        <v>0</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW78">
+        <v>0</v>
+      </c>
+      <c r="AX78">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ78" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA78" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB78">
+        <v>0</v>
+      </c>
+      <c r="BC78">
+        <v>0</v>
+      </c>
+      <c r="BD78">
+        <v>0</v>
+      </c>
+      <c r="BE78">
+        <v>1</v>
+      </c>
+      <c r="BF78" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG78" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH78" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI78">
+        <v>0</v>
+      </c>
+      <c r="BJ78" s="46" t="s">
+        <v>1902</v>
+      </c>
+      <c r="BK78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:63">
+      <c r="A79" s="44" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>3</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+      <c r="AB79">
+        <v>1</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>-1</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>10</v>
+      </c>
+      <c r="AG79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI79" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AJ79" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AK79" s="44" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AL79" s="44">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="44" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AN79" s="44">
+        <v>1</v>
+      </c>
+      <c r="AO79" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP79" s="44">
+        <v>0</v>
+      </c>
+      <c r="AQ79">
+        <v>0</v>
+      </c>
+      <c r="AR79">
+        <v>0</v>
+      </c>
+      <c r="AS79">
+        <v>1</v>
+      </c>
+      <c r="AT79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU79">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW79">
+        <v>0</v>
+      </c>
+      <c r="AX79">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ79" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA79" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB79">
+        <v>0</v>
+      </c>
+      <c r="BC79">
+        <v>0</v>
+      </c>
+      <c r="BD79">
+        <v>0</v>
+      </c>
+      <c r="BE79">
+        <v>1</v>
+      </c>
+      <c r="BF79" t="s">
+        <v>1762</v>
+      </c>
+      <c r="BG79" t="s">
+        <v>36</v>
+      </c>
+      <c r="BH79" t="s">
+        <v>1659</v>
+      </c>
+      <c r="BI79">
+        <v>0</v>
+      </c>
+      <c r="BJ79" s="46" t="s">
         <v>1944</v>
       </c>
-      <c r="BK77" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="78" spans="1:63">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-      <c r="Q78" s="3"/>
-      <c r="R78" s="3"/>
-      <c r="S78" s="3"/>
-      <c r="T78" s="3"/>
-      <c r="BJ78" s="46"/>
-    </row>
-    <row r="79" spans="1:63">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="3"/>
-      <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
+      <c r="BK79" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="80" spans="1:63">
       <c r="A80" s="3"/>
@@ -79422,6 +79794,7 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
+      <c r="BJ80" s="46"/>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" s="3"/>
@@ -80016,6 +80389,50 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
+    </row>
+    <row r="108" spans="1:20">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="3"/>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3"/>
+      <c r="S108" s="3"/>
+      <c r="T108" s="3"/>
+    </row>
+    <row r="109" spans="1:20">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
+      <c r="R109" s="3"/>
+      <c r="S109" s="3"/>
+      <c r="T109" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8D07A7-4EBB-4F7F-8BBE-DA7BE2642DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C2DE45-458C-4364-ACCD-FA5A93D3B04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="5" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11092" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11273" uniqueCount="2077">
   <si>
     <t>NAME</t>
   </si>
@@ -6352,6 +6352,69 @@
   </si>
   <si>
     <t>guts,1</t>
+  </si>
+  <si>
+    <t>--------------------------------------JUST RESOURCES---------------------------------------------------</t>
+  </si>
+  <si>
+    <t>iron_ore</t>
+  </si>
+  <si>
+    <t>silver_shards</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>obsidian</t>
+  </si>
+  <si>
+    <t>moonstone_dust</t>
+  </si>
+  <si>
+    <t>froststone</t>
+  </si>
+  <si>
+    <t>darkstone</t>
+  </si>
+  <si>
+    <t>bronze_ore</t>
+  </si>
+  <si>
+    <t>sunstone</t>
+  </si>
+  <si>
+    <t>amber_shards</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>flax</t>
+  </si>
+  <si>
+    <t>green_berry</t>
+  </si>
+  <si>
+    <t>red_apple</t>
+  </si>
+  <si>
+    <t>almond</t>
+  </si>
+  <si>
+    <t>honeycomb</t>
+  </si>
+  <si>
+    <t>cotton</t>
+  </si>
+  <si>
+    <t>corn</t>
+  </si>
+  <si>
+    <t>coconut_milk</t>
+  </si>
+  <si>
+    <t>soybeans</t>
   </si>
 </sst>
 </file>
@@ -56690,7 +56753,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
@@ -64700,77 +64763,1972 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" ht="14">
+      <c r="A91" s="55" t="s">
+        <v>2056</v>
+      </c>
       <c r="AE91" s="3"/>
       <c r="AF91" s="3"/>
     </row>
-    <row r="92" spans="1:32">
-      <c r="AE92" s="3"/>
-      <c r="AF92" s="3"/>
-    </row>
-    <row r="93" spans="1:32">
-      <c r="AE93" s="3"/>
-      <c r="AF93" s="3"/>
-    </row>
-    <row r="94" spans="1:32">
-      <c r="AE94" s="3"/>
-      <c r="AF94" s="3"/>
-    </row>
-    <row r="95" spans="1:32">
-      <c r="AE95" s="3"/>
-      <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="1:32">
-      <c r="AE96" s="3"/>
-      <c r="AF96" s="3"/>
-    </row>
-    <row r="97" spans="31:32">
-      <c r="AE97" s="3"/>
-      <c r="AF97" s="3"/>
-    </row>
-    <row r="98" spans="31:32">
-      <c r="AE98" s="3"/>
-      <c r="AF98" s="3"/>
-    </row>
-    <row r="99" spans="31:32">
-      <c r="AE99" s="3"/>
-      <c r="AF99" s="3"/>
-    </row>
-    <row r="100" spans="31:32">
-      <c r="AE100" s="3"/>
-      <c r="AF100" s="3"/>
-    </row>
-    <row r="101" spans="31:32">
-      <c r="AE101" s="3"/>
-      <c r="AF101" s="3"/>
-    </row>
-    <row r="102" spans="31:32">
-      <c r="AE102" s="3"/>
-      <c r="AF102" s="3"/>
-    </row>
-    <row r="103" spans="31:32">
-      <c r="AE103" s="3"/>
-      <c r="AF103" s="3"/>
-    </row>
-    <row r="104" spans="31:32">
-      <c r="AE104" s="3"/>
-      <c r="AF104" s="3"/>
-    </row>
-    <row r="105" spans="31:32">
-      <c r="AE105" s="3"/>
-      <c r="AF105" s="3"/>
-    </row>
-    <row r="106" spans="31:32">
-      <c r="AE106" s="3"/>
-      <c r="AF106" s="3"/>
-    </row>
-    <row r="107" spans="31:32">
-      <c r="AE107" s="3"/>
-      <c r="AF107" s="3"/>
-    </row>
-    <row r="108" spans="31:32">
-      <c r="AE108" s="3"/>
-      <c r="AF108" s="3"/>
+    <row r="92" spans="1:32" ht="13">
+      <c r="A92" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B92" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C92" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E92" s="44">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <v>0</v>
+      </c>
+      <c r="U92">
+        <v>10</v>
+      </c>
+      <c r="V92" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92">
+        <v>1</v>
+      </c>
+      <c r="Y92" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA92">
+        <v>11</v>
+      </c>
+      <c r="AB92" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD92">
+        <v>5</v>
+      </c>
+      <c r="AE92">
+        <v>0</v>
+      </c>
+      <c r="AF92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32" ht="13">
+      <c r="A93" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B93" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C93" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D93" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E93" s="44">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>0</v>
+      </c>
+      <c r="U93">
+        <v>10</v>
+      </c>
+      <c r="V93" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93">
+        <v>1</v>
+      </c>
+      <c r="Y93" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA93">
+        <v>11</v>
+      </c>
+      <c r="AB93" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD93">
+        <v>5</v>
+      </c>
+      <c r="AE93">
+        <v>0</v>
+      </c>
+      <c r="AF93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32" ht="13">
+      <c r="A94" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B94" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C94" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D94" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E94" s="44">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>0</v>
+      </c>
+      <c r="U94">
+        <v>10</v>
+      </c>
+      <c r="V94" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+      <c r="Y94" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA94">
+        <v>11</v>
+      </c>
+      <c r="AB94" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD94">
+        <v>5</v>
+      </c>
+      <c r="AE94">
+        <v>0</v>
+      </c>
+      <c r="AF94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32" ht="13">
+      <c r="A95" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B95" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C95" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E95" s="44">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <v>0</v>
+      </c>
+      <c r="U95">
+        <v>10</v>
+      </c>
+      <c r="V95" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W95">
+        <v>0</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA95">
+        <v>11</v>
+      </c>
+      <c r="AB95" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD95">
+        <v>5</v>
+      </c>
+      <c r="AE95">
+        <v>0</v>
+      </c>
+      <c r="AF95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32" ht="13">
+      <c r="A96" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B96" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C96" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E96" s="44">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>0</v>
+      </c>
+      <c r="T96">
+        <v>0</v>
+      </c>
+      <c r="U96">
+        <v>10</v>
+      </c>
+      <c r="V96" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W96">
+        <v>0</v>
+      </c>
+      <c r="X96">
+        <v>1</v>
+      </c>
+      <c r="Y96" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA96">
+        <v>11</v>
+      </c>
+      <c r="AB96" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD96">
+        <v>5</v>
+      </c>
+      <c r="AE96">
+        <v>0</v>
+      </c>
+      <c r="AF96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:32" ht="13">
+      <c r="A97" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B97" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C97" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D97" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E97" s="44">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>0</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97">
+        <v>10</v>
+      </c>
+      <c r="V97" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W97">
+        <v>0</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="Y97" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA97">
+        <v>11</v>
+      </c>
+      <c r="AB97" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD97">
+        <v>5</v>
+      </c>
+      <c r="AE97">
+        <v>0</v>
+      </c>
+      <c r="AF97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:32" ht="13">
+      <c r="A98" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B98" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C98" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D98" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" s="44">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>0</v>
+      </c>
+      <c r="T98">
+        <v>0</v>
+      </c>
+      <c r="U98">
+        <v>10</v>
+      </c>
+      <c r="V98" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W98">
+        <v>0</v>
+      </c>
+      <c r="X98">
+        <v>1</v>
+      </c>
+      <c r="Y98" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA98">
+        <v>11</v>
+      </c>
+      <c r="AB98" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD98">
+        <v>5</v>
+      </c>
+      <c r="AE98">
+        <v>0</v>
+      </c>
+      <c r="AF98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:32" ht="13">
+      <c r="A99" s="1" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B99" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C99" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E99" s="44">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>0</v>
+      </c>
+      <c r="T99">
+        <v>0</v>
+      </c>
+      <c r="U99">
+        <v>10</v>
+      </c>
+      <c r="V99" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W99">
+        <v>0</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="Y99" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA99">
+        <v>11</v>
+      </c>
+      <c r="AB99" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD99">
+        <v>5</v>
+      </c>
+      <c r="AE99">
+        <v>0</v>
+      </c>
+      <c r="AF99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32" ht="13">
+      <c r="A100" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B100" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C100" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D100" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" s="44">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100">
+        <v>0</v>
+      </c>
+      <c r="T100">
+        <v>0</v>
+      </c>
+      <c r="U100">
+        <v>10</v>
+      </c>
+      <c r="V100" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W100">
+        <v>0</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA100">
+        <v>11</v>
+      </c>
+      <c r="AB100" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD100">
+        <v>5</v>
+      </c>
+      <c r="AE100">
+        <v>0</v>
+      </c>
+      <c r="AF100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32" ht="13">
+      <c r="A101" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B101" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C101" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="44">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101">
+        <v>0</v>
+      </c>
+      <c r="T101">
+        <v>0</v>
+      </c>
+      <c r="U101">
+        <v>10</v>
+      </c>
+      <c r="V101" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W101">
+        <v>0</v>
+      </c>
+      <c r="X101">
+        <v>1</v>
+      </c>
+      <c r="Y101" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA101">
+        <v>11</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD101">
+        <v>5</v>
+      </c>
+      <c r="AE101">
+        <v>0</v>
+      </c>
+      <c r="AF101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:32" ht="13">
+      <c r="A102" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B102" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C102" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" s="44">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>0</v>
+      </c>
+      <c r="U102">
+        <v>10</v>
+      </c>
+      <c r="V102" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W102">
+        <v>0</v>
+      </c>
+      <c r="X102">
+        <v>1</v>
+      </c>
+      <c r="Y102" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA102">
+        <v>11</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD102">
+        <v>5</v>
+      </c>
+      <c r="AE102">
+        <v>0</v>
+      </c>
+      <c r="AF102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:32" ht="13">
+      <c r="A103" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B103" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C103" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D103" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E103" s="44">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>0</v>
+      </c>
+      <c r="U103">
+        <v>10</v>
+      </c>
+      <c r="V103" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W103">
+        <v>0</v>
+      </c>
+      <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA103">
+        <v>11</v>
+      </c>
+      <c r="AB103" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD103">
+        <v>5</v>
+      </c>
+      <c r="AE103">
+        <v>0</v>
+      </c>
+      <c r="AF103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:32" ht="13">
+      <c r="A104" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B104" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C104" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D104" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E104" s="44">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>0</v>
+      </c>
+      <c r="R104">
+        <v>0</v>
+      </c>
+      <c r="S104">
+        <v>0</v>
+      </c>
+      <c r="T104">
+        <v>0</v>
+      </c>
+      <c r="U104">
+        <v>10</v>
+      </c>
+      <c r="V104" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W104">
+        <v>0</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA104">
+        <v>11</v>
+      </c>
+      <c r="AB104" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD104">
+        <v>5</v>
+      </c>
+      <c r="AE104">
+        <v>0</v>
+      </c>
+      <c r="AF104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:32" ht="13">
+      <c r="A105" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B105" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C105" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E105" s="44">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+      <c r="R105">
+        <v>0</v>
+      </c>
+      <c r="S105">
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105">
+        <v>10</v>
+      </c>
+      <c r="V105" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W105">
+        <v>0</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA105">
+        <v>11</v>
+      </c>
+      <c r="AB105" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD105">
+        <v>5</v>
+      </c>
+      <c r="AE105">
+        <v>0</v>
+      </c>
+      <c r="AF105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:32" ht="13">
+      <c r="A106" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B106" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C106" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D106" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" s="44">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>0</v>
+      </c>
+      <c r="R106">
+        <v>0</v>
+      </c>
+      <c r="S106">
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <v>0</v>
+      </c>
+      <c r="U106">
+        <v>10</v>
+      </c>
+      <c r="V106" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W106">
+        <v>0</v>
+      </c>
+      <c r="X106">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA106">
+        <v>11</v>
+      </c>
+      <c r="AB106" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD106">
+        <v>5</v>
+      </c>
+      <c r="AE106">
+        <v>0</v>
+      </c>
+      <c r="AF106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:32" ht="13">
+      <c r="A107" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B107" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C107" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D107" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" s="44">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>0</v>
+      </c>
+      <c r="R107">
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+      <c r="U107">
+        <v>10</v>
+      </c>
+      <c r="V107" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
+      </c>
+      <c r="X107">
+        <v>1</v>
+      </c>
+      <c r="Y107" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA107">
+        <v>11</v>
+      </c>
+      <c r="AB107" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD107">
+        <v>5</v>
+      </c>
+      <c r="AE107">
+        <v>0</v>
+      </c>
+      <c r="AF107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:32" ht="13">
+      <c r="A108" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B108" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C108" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D108" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108" s="44">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108">
+        <v>0</v>
+      </c>
+      <c r="S108">
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <v>0</v>
+      </c>
+      <c r="U108">
+        <v>10</v>
+      </c>
+      <c r="V108" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W108">
+        <v>0</v>
+      </c>
+      <c r="X108">
+        <v>1</v>
+      </c>
+      <c r="Y108" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA108">
+        <v>11</v>
+      </c>
+      <c r="AB108" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC108" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD108">
+        <v>5</v>
+      </c>
+      <c r="AE108">
+        <v>0</v>
+      </c>
+      <c r="AF108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:32" ht="13">
+      <c r="A109" s="1" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B109" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C109" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D109" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E109" s="44">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109">
+        <v>0</v>
+      </c>
+      <c r="S109">
+        <v>0</v>
+      </c>
+      <c r="T109">
+        <v>0</v>
+      </c>
+      <c r="U109">
+        <v>10</v>
+      </c>
+      <c r="V109" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W109">
+        <v>0</v>
+      </c>
+      <c r="X109">
+        <v>1</v>
+      </c>
+      <c r="Y109" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA109">
+        <v>11</v>
+      </c>
+      <c r="AB109" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC109" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD109">
+        <v>5</v>
+      </c>
+      <c r="AE109">
+        <v>0</v>
+      </c>
+      <c r="AF109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:32" ht="13">
+      <c r="A110" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B110" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C110" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D110" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E110" s="44">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110">
+        <v>10</v>
+      </c>
+      <c r="V110" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W110">
+        <v>0</v>
+      </c>
+      <c r="X110">
+        <v>1</v>
+      </c>
+      <c r="Y110" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA110">
+        <v>11</v>
+      </c>
+      <c r="AB110" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD110">
+        <v>5</v>
+      </c>
+      <c r="AE110">
+        <v>0</v>
+      </c>
+      <c r="AF110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:32" ht="13">
+      <c r="A111" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B111" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C111" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D111" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" s="44">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111">
+        <v>0</v>
+      </c>
+      <c r="S111">
+        <v>0</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+      <c r="U111">
+        <v>10</v>
+      </c>
+      <c r="V111" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="W111">
+        <v>0</v>
+      </c>
+      <c r="X111">
+        <v>1</v>
+      </c>
+      <c r="Y111" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA111">
+        <v>11</v>
+      </c>
+      <c r="AB111" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AC111" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD111">
+        <v>5</v>
+      </c>
+      <c r="AE111">
+        <v>0</v>
+      </c>
+      <c r="AF111">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B6914B-5353-4B9B-92A3-5B4411E286A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F023065A-2246-4E11-8911-AF714CA7C393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,6 +44,7 @@
     <sheet name="DYNAMIC_ID" sheetId="30" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60625,7 +60626,7 @@
         <v>36</v>
       </c>
       <c r="AE36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -60726,7 +60727,7 @@
         <v>36</v>
       </c>
       <c r="AE37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -60827,7 +60828,7 @@
         <v>36</v>
       </c>
       <c r="AE38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -60928,7 +60929,7 @@
         <v>36</v>
       </c>
       <c r="AE39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF39">
         <v>0</v>
@@ -61029,7 +61030,7 @@
         <v>36</v>
       </c>
       <c r="AE40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF40">
         <v>5</v>
@@ -61130,7 +61131,7 @@
         <v>36</v>
       </c>
       <c r="AE41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -61231,7 +61232,7 @@
         <v>36</v>
       </c>
       <c r="AE42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF42">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_exp.xlsx
+++ b/Assets/StreamingAssets/Config_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F023065A-2246-4E11-8911-AF714CA7C393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81DE2F7-C94E-43C5-8FBC-08FEAC4E083F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11455" uniqueCount="2097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11769" uniqueCount="2100">
   <si>
     <t>NAME</t>
   </si>
@@ -6476,13 +6476,22 @@
   </si>
   <si>
     <t>pumpkin</t>
+  </si>
+  <si>
+    <t>UPGRADE_COST</t>
+  </si>
+  <si>
+    <t>iron_ore,1#silver_shards,1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -6645,8 +6654,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6718,6 +6734,11 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -6748,11 +6769,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -6850,8 +6872,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="2" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -7112,7 +7136,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BL998"/>
+  <dimension ref="A1:BM998"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.453125" customWidth="1"/>
@@ -7122,8 +7146,8 @@
     <col min="7" max="7" width="8.90625" customWidth="1"/>
     <col min="8" max="8" width="10.08984375" customWidth="1"/>
     <col min="9" max="9" width="11.6328125" customWidth="1"/>
-    <col min="10" max="10" width="13.08984375" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" customWidth="1"/>
+    <col min="11" max="11" width="8.453125" customWidth="1"/>
     <col min="12" max="12" width="8.90625" customWidth="1"/>
     <col min="13" max="13" width="12.26953125" customWidth="1"/>
     <col min="14" max="14" width="9.7265625" customWidth="1"/>
@@ -7163,9 +7187,10 @@
     <col min="62" max="62" width="15.08984375" customWidth="1"/>
     <col min="63" max="63" width="17.1796875" customWidth="1"/>
     <col min="64" max="64" width="15.36328125" customWidth="1"/>
+    <col min="65" max="65" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="15.75" customHeight="1">
+    <row r="1" spans="1:65" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7358,8 +7383,11 @@
       <c r="BL1" s="43" t="s">
         <v>1947</v>
       </c>
-    </row>
-    <row r="2" spans="1:64" ht="12.5">
+      <c r="BM1" s="43" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" ht="12.5">
       <c r="A2" s="47" t="s">
         <v>954</v>
       </c>
@@ -7552,8 +7580,11 @@
       <c r="BL2" t="s">
         <v>1657</v>
       </c>
-    </row>
-    <row r="3" spans="1:64" ht="12.5">
+      <c r="BM2" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" ht="12.5">
       <c r="A3" s="47" t="s">
         <v>1406</v>
       </c>
@@ -7746,8 +7777,11 @@
       <c r="BL3" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="4" spans="1:64" ht="12.5">
+      <c r="BM3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:65" ht="12.5">
       <c r="A4" s="47" t="s">
         <v>1766</v>
       </c>
@@ -7940,8 +7974,11 @@
       <c r="BL4" t="s">
         <v>1659</v>
       </c>
-    </row>
-    <row r="5" spans="1:64" ht="12.5">
+      <c r="BM4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:65" ht="12.5">
       <c r="A5" s="47" t="s">
         <v>1767</v>
       </c>
@@ -8134,8 +8171,11 @@
       <c r="BL5" t="s">
         <v>1660</v>
       </c>
-    </row>
-    <row r="6" spans="1:64" ht="12.5">
+      <c r="BM5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:65" ht="12.5">
       <c r="A6" s="47" t="s">
         <v>1466</v>
       </c>
@@ -8328,8 +8368,11 @@
       <c r="BL6" t="s">
         <v>1660</v>
       </c>
-    </row>
-    <row r="7" spans="1:64" ht="12.5">
+      <c r="BM6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:65" ht="12.5">
       <c r="A7" s="47" t="s">
         <v>1467</v>
       </c>
@@ -8522,8 +8565,11 @@
       <c r="BL7" t="s">
         <v>1661</v>
       </c>
-    </row>
-    <row r="8" spans="1:64" ht="12.5">
+      <c r="BM7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:65" ht="12.5">
       <c r="A8" s="47" t="s">
         <v>43</v>
       </c>
@@ -8716,8 +8762,11 @@
       <c r="BL8" t="s">
         <v>1662</v>
       </c>
-    </row>
-    <row r="9" spans="1:64" ht="12.5">
+      <c r="BM8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:65" ht="12.5">
       <c r="A9" s="47" t="s">
         <v>1509</v>
       </c>
@@ -8910,8 +8959,11 @@
       <c r="BL9" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="10" spans="1:64" ht="12.5">
+      <c r="BM9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:65" ht="12.5">
       <c r="A10" s="47" t="s">
         <v>1510</v>
       </c>
@@ -9104,8 +9156,11 @@
       <c r="BL10" t="s">
         <v>1664</v>
       </c>
-    </row>
-    <row r="11" spans="1:64" ht="12.5">
+      <c r="BM10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:65" ht="12.5">
       <c r="A11" s="47" t="s">
         <v>1521</v>
       </c>
@@ -9298,8 +9353,11 @@
       <c r="BL11" t="s">
         <v>1665</v>
       </c>
-    </row>
-    <row r="12" spans="1:64" ht="12.5">
+      <c r="BM11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:65" ht="12.5">
       <c r="A12" s="47" t="s">
         <v>1522</v>
       </c>
@@ -9492,8 +9550,11 @@
       <c r="BL12" t="s">
         <v>1666</v>
       </c>
-    </row>
-    <row r="13" spans="1:64" ht="12.5">
+      <c r="BM12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:65" ht="12.5">
       <c r="A13" s="47" t="s">
         <v>1550</v>
       </c>
@@ -9686,8 +9747,11 @@
       <c r="BL13" t="s">
         <v>1667</v>
       </c>
-    </row>
-    <row r="14" spans="1:64" ht="12.5">
+      <c r="BM13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:65" ht="12.5">
       <c r="A14" s="47" t="s">
         <v>1578</v>
       </c>
@@ -9880,8 +9944,11 @@
       <c r="BL14" t="s">
         <v>1668</v>
       </c>
-    </row>
-    <row r="15" spans="1:64" ht="12.5">
+      <c r="BM14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:65" ht="12.5">
       <c r="A15" s="47" t="s">
         <v>1601</v>
       </c>
@@ -10074,8 +10141,11 @@
       <c r="BL15" t="s">
         <v>1669</v>
       </c>
-    </row>
-    <row r="16" spans="1:64" ht="12.5">
+      <c r="BM15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:65" ht="12.5">
       <c r="A16" s="47" t="s">
         <v>34</v>
       </c>
@@ -10268,8 +10338,11 @@
       <c r="BL16" t="s">
         <v>1670</v>
       </c>
-    </row>
-    <row r="17" spans="1:64" ht="12.5">
+      <c r="BM16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:65" ht="12.5">
       <c r="A17" s="47" t="s">
         <v>1370</v>
       </c>
@@ -10462,8 +10535,11 @@
       <c r="BL17" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="18" spans="1:64" ht="12.5">
+      <c r="BM17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:65" ht="12.5">
       <c r="A18" s="47" t="s">
         <v>1165</v>
       </c>
@@ -10656,8 +10732,11 @@
       <c r="BL18" t="s">
         <v>1672</v>
       </c>
-    </row>
-    <row r="19" spans="1:64" ht="12.5">
+      <c r="BM18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:65" ht="12.5">
       <c r="A19" s="47" t="s">
         <v>1619</v>
       </c>
@@ -10850,8 +10929,11 @@
       <c r="BL19" t="s">
         <v>1673</v>
       </c>
-    </row>
-    <row r="20" spans="1:64" ht="12.5">
+      <c r="BM19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:65" ht="12.5">
       <c r="A20" s="47" t="s">
         <v>1632</v>
       </c>
@@ -11044,8 +11126,11 @@
       <c r="BL20" t="s">
         <v>1674</v>
       </c>
-    </row>
-    <row r="21" spans="1:64" ht="12.5">
+      <c r="BM20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:65" ht="12.5">
       <c r="A21" s="47" t="s">
         <v>1258</v>
       </c>
@@ -11238,8 +11323,11 @@
       <c r="BL21" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="22" spans="1:64" ht="12.5">
+      <c r="BM21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:65" ht="12.5">
       <c r="A22" s="47" t="s">
         <v>1716</v>
       </c>
@@ -11432,8 +11520,11 @@
       <c r="BL22" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="23" spans="1:64" ht="12.5">
+      <c r="BM22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:65" ht="12.5">
       <c r="A23" s="47" t="s">
         <v>1736</v>
       </c>
@@ -11626,8 +11717,11 @@
       <c r="BL23" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="24" spans="1:64" ht="12.5">
+      <c r="BM23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:65" ht="12.5">
       <c r="A24" s="47" t="s">
         <v>1737</v>
       </c>
@@ -11820,8 +11914,11 @@
       <c r="BL24" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="25" spans="1:64" ht="12.5">
+      <c r="BM24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:65" ht="12.5">
       <c r="A25" s="47" t="s">
         <v>1739</v>
       </c>
@@ -12014,8 +12111,11 @@
       <c r="BL25" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="26" spans="1:64" ht="12.5">
+      <c r="BM25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:65" ht="12.5">
       <c r="A26" s="47" t="s">
         <v>1738</v>
       </c>
@@ -12208,8 +12308,11 @@
       <c r="BL26" t="s">
         <v>1559</v>
       </c>
-    </row>
-    <row r="27" spans="1:64" ht="12.5">
+      <c r="BM26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:65" ht="12.5">
       <c r="A27" s="47" t="s">
         <v>52</v>
       </c>
@@ -12402,8 +12505,11 @@
       <c r="BL27" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="28" spans="1:64" ht="12.5">
+      <c r="BM27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:65" ht="12.5">
       <c r="A28" s="47" t="s">
         <v>1728</v>
       </c>
@@ -12596,8 +12702,11 @@
       <c r="BL28" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="29" spans="1:64" ht="14">
+      <c r="BM28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:65" ht="14">
       <c r="A29" s="54" t="s">
         <v>1816</v>
       </c>
@@ -12790,8 +12899,11 @@
       <c r="BL29" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="30" spans="1:64" ht="12.5">
+      <c r="BM29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:65" ht="12.5">
       <c r="A30" s="47" t="s">
         <v>1817</v>
       </c>
@@ -12984,8 +13096,11 @@
       <c r="BL30" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="31" spans="1:64" ht="12.5">
+      <c r="BM30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:65" ht="12.5">
       <c r="A31" s="47" t="s">
         <v>1818</v>
       </c>
@@ -13178,8 +13293,11 @@
       <c r="BL31" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="32" spans="1:64" ht="12.5">
+      <c r="BM31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:65" ht="12.5">
       <c r="A32" s="47" t="s">
         <v>1819</v>
       </c>
@@ -13372,8 +13490,11 @@
       <c r="BL32" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="33" spans="1:64" ht="12.5">
+      <c r="BM32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:65" ht="12.5">
       <c r="A33" s="47" t="s">
         <v>1820</v>
       </c>
@@ -13566,8 +13687,11 @@
       <c r="BL33" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="34" spans="1:64" ht="12.5">
+      <c r="BM33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:65" ht="12.5">
       <c r="A34" s="47" t="s">
         <v>1821</v>
       </c>
@@ -13760,8 +13884,11 @@
       <c r="BL34" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="35" spans="1:64" ht="12.5">
+      <c r="BM34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:65" ht="12.5">
       <c r="A35" s="47" t="s">
         <v>1822</v>
       </c>
@@ -13954,8 +14081,11 @@
       <c r="BL35" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="36" spans="1:64" ht="12.5">
+      <c r="BM35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:65" ht="12.5">
       <c r="A36" s="47" t="s">
         <v>1823</v>
       </c>
@@ -14148,8 +14278,11 @@
       <c r="BL36" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="37" spans="1:64" ht="12.5">
+      <c r="BM36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:65" ht="12.5">
       <c r="A37" s="47" t="s">
         <v>1824</v>
       </c>
@@ -14342,8 +14475,11 @@
       <c r="BL37" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="38" spans="1:64" ht="12.5">
+      <c r="BM37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:65" ht="12.5">
       <c r="A38" s="47" t="s">
         <v>1825</v>
       </c>
@@ -14536,8 +14672,11 @@
       <c r="BL38" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="39" spans="1:64" ht="12.5">
+      <c r="BM38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:65" ht="12.5">
       <c r="A39" s="47" t="s">
         <v>1826</v>
       </c>
@@ -14730,8 +14869,11 @@
       <c r="BL39" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="40" spans="1:64" ht="12.5">
+      <c r="BM39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:65" ht="12.5">
       <c r="A40" s="47" t="s">
         <v>1827</v>
       </c>
@@ -14924,8 +15066,11 @@
       <c r="BL40" t="s">
         <v>1559</v>
       </c>
-    </row>
-    <row r="41" spans="1:64" ht="12.5">
+      <c r="BM40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:65" ht="12.5">
       <c r="A41" s="47" t="s">
         <v>1828</v>
       </c>
@@ -15118,8 +15263,11 @@
       <c r="BL41" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="42" spans="1:64" ht="12.5">
+      <c r="BM41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:65" ht="12.5">
       <c r="A42" s="47" t="s">
         <v>1829</v>
       </c>
@@ -15312,8 +15460,11 @@
       <c r="BL42" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="43" spans="1:64" ht="12.5">
+      <c r="BM42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:65" ht="12.5">
       <c r="A43" s="47" t="s">
         <v>1830</v>
       </c>
@@ -15506,8 +15657,11 @@
       <c r="BL43" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="44" spans="1:64" ht="12.5">
+      <c r="BM43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:65" ht="12.5">
       <c r="A44" s="47" t="s">
         <v>1831</v>
       </c>
@@ -15700,8 +15854,11 @@
       <c r="BL44" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="45" spans="1:64" ht="12.5">
+      <c r="BM44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:65" ht="12.5">
       <c r="A45" s="47" t="s">
         <v>1832</v>
       </c>
@@ -15894,8 +16051,11 @@
       <c r="BL45" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="46" spans="1:64" ht="12.5">
+      <c r="BM45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:65" ht="12.5">
       <c r="A46" s="47" t="s">
         <v>1833</v>
       </c>
@@ -16088,8 +16248,11 @@
       <c r="BL46" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="47" spans="1:64" ht="12.5">
+      <c r="BM46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:65" ht="12.5">
       <c r="A47" s="47" t="s">
         <v>1834</v>
       </c>
@@ -16282,8 +16445,11 @@
       <c r="BL47" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="48" spans="1:64" ht="12.5">
+      <c r="BM47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:65" ht="12.5">
       <c r="A48" s="47" t="s">
         <v>1835</v>
       </c>
@@ -16476,8 +16642,11 @@
       <c r="BL48" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="49" spans="1:64" ht="12.5">
+      <c r="BM48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:65" ht="12.5">
       <c r="A49" s="47" t="s">
         <v>1836</v>
       </c>
@@ -16670,8 +16839,11 @@
       <c r="BL49" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="50" spans="1:64" ht="12.5">
+      <c r="BM49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:65" ht="12.5">
       <c r="A50" s="47" t="s">
         <v>1837</v>
       </c>
@@ -16864,8 +17036,11 @@
       <c r="BL50" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="51" spans="1:64" ht="12.5">
+      <c r="BM50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:65" ht="12.5">
       <c r="A51" s="47" t="s">
         <v>1838</v>
       </c>
@@ -17058,8 +17233,11 @@
       <c r="BL51" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="52" spans="1:64" ht="12.5">
+      <c r="BM51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:65" ht="12.5">
       <c r="A52" s="47" t="s">
         <v>1839</v>
       </c>
@@ -17252,8 +17430,11 @@
       <c r="BL52" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="53" spans="1:64" ht="12.5">
+      <c r="BM52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:65" ht="12.5">
       <c r="A53" s="47" t="s">
         <v>1840</v>
       </c>
@@ -17446,8 +17627,11 @@
       <c r="BL53" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="54" spans="1:64" ht="12.5">
+      <c r="BM53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:65" ht="12.5">
       <c r="A54" s="47" t="s">
         <v>1841</v>
       </c>
@@ -17640,8 +17824,11 @@
       <c r="BL54" t="s">
         <v>1559</v>
       </c>
-    </row>
-    <row r="55" spans="1:64" ht="12.5">
+      <c r="BM54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:65" ht="12.5">
       <c r="A55" s="47" t="s">
         <v>1842</v>
       </c>
@@ -17834,8 +18021,11 @@
       <c r="BL55" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="56" spans="1:64" ht="12.5">
+      <c r="BM55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:65" ht="12.5">
       <c r="A56" s="47" t="s">
         <v>1843</v>
       </c>
@@ -18028,8 +18218,11 @@
       <c r="BL56" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="57" spans="1:64" ht="12.5">
+      <c r="BM56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:65" ht="12.5">
       <c r="A57" s="47" t="s">
         <v>1844</v>
       </c>
@@ -18222,8 +18415,11 @@
       <c r="BL57" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="58" spans="1:64" ht="12.5">
+      <c r="BM57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:65" ht="12.5">
       <c r="A58" s="47" t="s">
         <v>1845</v>
       </c>
@@ -18416,8 +18612,11 @@
       <c r="BL58" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="59" spans="1:64" ht="12.5">
+      <c r="BM58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:65" ht="12.5">
       <c r="A59" s="47" t="s">
         <v>1846</v>
       </c>
@@ -18610,8 +18809,11 @@
       <c r="BL59" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="60" spans="1:64" ht="12.5">
+      <c r="BM59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:65" ht="12.5">
       <c r="A60" s="47" t="s">
         <v>1847</v>
       </c>
@@ -18804,8 +19006,11 @@
       <c r="BL60" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="61" spans="1:64" ht="12.5">
+      <c r="BM60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:65" ht="12.5">
       <c r="A61" s="47" t="s">
         <v>1848</v>
       </c>
@@ -18998,8 +19203,11 @@
       <c r="BL61" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="62" spans="1:64" ht="12.5">
+      <c r="BM61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:65" ht="12.5">
       <c r="A62" s="47" t="s">
         <v>1849</v>
       </c>
@@ -19192,8 +19400,11 @@
       <c r="BL62" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="63" spans="1:64" ht="12.5">
+      <c r="BM62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:65" ht="12.5">
       <c r="A63" s="47" t="s">
         <v>1850</v>
       </c>
@@ -19386,8 +19597,11 @@
       <c r="BL63" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="64" spans="1:64" ht="12.5">
+      <c r="BM63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:65" ht="12.5">
       <c r="A64" s="47" t="s">
         <v>1851</v>
       </c>
@@ -19580,8 +19794,11 @@
       <c r="BL64" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="65" spans="1:64" ht="12.5">
+      <c r="BM64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:65" ht="12.5">
       <c r="A65" s="47" t="s">
         <v>1852</v>
       </c>
@@ -19774,8 +19991,11 @@
       <c r="BL65" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="66" spans="1:64" ht="12.5">
+      <c r="BM65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:65" ht="12.5">
       <c r="A66" s="47" t="s">
         <v>1853</v>
       </c>
@@ -19968,8 +20188,11 @@
       <c r="BL66" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="67" spans="1:64" ht="12.5">
+      <c r="BM66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:65" ht="12.5">
       <c r="A67" s="47" t="s">
         <v>1854</v>
       </c>
@@ -20162,8 +20385,11 @@
       <c r="BL67" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="68" spans="1:64" ht="12.5">
+      <c r="BM67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:65" ht="12.5">
       <c r="A68" s="47" t="s">
         <v>1855</v>
       </c>
@@ -20356,8 +20582,11 @@
       <c r="BL68" t="s">
         <v>1559</v>
       </c>
-    </row>
-    <row r="69" spans="1:64" ht="12.5">
+      <c r="BM68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:65" ht="12.5">
       <c r="A69" s="47" t="s">
         <v>1856</v>
       </c>
@@ -20550,8 +20779,11 @@
       <c r="BL69" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="70" spans="1:64" ht="12.5">
+      <c r="BM69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:65" ht="12.5">
       <c r="A70" s="47" t="s">
         <v>1857</v>
       </c>
@@ -20744,8 +20976,11 @@
       <c r="BL70" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="71" spans="1:64" ht="12.5">
+      <c r="BM70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:65" ht="12.5">
       <c r="A71" s="47" t="s">
         <v>1858</v>
       </c>
@@ -20938,8 +21173,11 @@
       <c r="BL71" t="s">
         <v>1658</v>
       </c>
-    </row>
-    <row r="72" spans="1:64" ht="12.5">
+      <c r="BM71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:65" ht="12.5">
       <c r="A72" s="47" t="s">
         <v>1859</v>
       </c>
@@ -21132,8 +21370,11 @@
       <c r="BL72" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="73" spans="1:64" ht="12.5">
+      <c r="BM72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:65" ht="12.5">
       <c r="A73" s="47" t="s">
         <v>1860</v>
       </c>
@@ -21326,8 +21567,11 @@
       <c r="BL73" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="74" spans="1:64" ht="12.5">
+      <c r="BM73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:65" ht="12.5">
       <c r="A74" s="47" t="s">
         <v>1861</v>
       </c>
@@ -21520,8 +21764,11 @@
       <c r="BL74" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="75" spans="1:64" ht="12.5">
+      <c r="BM74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:65" ht="12.5">
       <c r="A75" s="47" t="s">
         <v>1862</v>
       </c>
@@ -21714,8 +21961,11 @@
       <c r="BL75" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="76" spans="1:64" ht="12.5">
+      <c r="BM75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:65" ht="12.5">
       <c r="A76" s="47" t="s">
         <v>1863</v>
       </c>
@@ -21908,8 +22158,11 @@
       <c r="BL76" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="77" spans="1:64" ht="12.5">
+      <c r="BM76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:65" ht="12.5">
       <c r="A77" s="47" t="s">
         <v>1864</v>
       </c>
@@ -22102,8 +22355,11 @@
       <c r="BL77" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="78" spans="1:64" ht="12.5">
+      <c r="BM77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:65" ht="12.5">
       <c r="A78" s="47" t="s">
         <v>1865</v>
       </c>
@@ -22296,8 +22552,11 @@
       <c r="BL78" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="79" spans="1:64" ht="14">
+      <c r="BM78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:65" ht="14">
       <c r="A79" s="55" t="s">
         <v>1890</v>
       </c>
@@ -22320,8 +22579,11 @@
       <c r="BL79" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="80" spans="1:64" ht="12.5">
+      <c r="BM79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:65" ht="12.5">
       <c r="A80" s="47" t="s">
         <v>1892</v>
       </c>
@@ -22514,8 +22776,11 @@
       <c r="BL80" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="81" spans="1:64" ht="12.5">
+      <c r="BM80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:65" ht="12.5">
       <c r="A81" s="47" t="s">
         <v>1893</v>
       </c>
@@ -22708,8 +22973,11 @@
       <c r="BL81" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="82" spans="1:64" ht="12.5">
+      <c r="BM81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:65" ht="12.5">
       <c r="A82" s="47" t="s">
         <v>1894</v>
       </c>
@@ -22902,8 +23170,11 @@
       <c r="BL82" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="83" spans="1:64" ht="12.5">
+      <c r="BM82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:65" ht="12.5">
       <c r="A83" s="47" t="s">
         <v>1895</v>
       </c>
@@ -23096,8 +23367,11 @@
       <c r="BL83" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="84" spans="1:64" ht="12.5">
+      <c r="BM83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:65" ht="12.5">
       <c r="A84" s="47" t="s">
         <v>1896</v>
       </c>
@@ -23290,74 +23564,77 @@
       <c r="BL84" t="s">
         <v>1663</v>
       </c>
-    </row>
-    <row r="85" spans="1:64" ht="12.5">
+      <c r="BM84" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:65" ht="12.5">
       <c r="K85" s="38"/>
       <c r="L85" s="38"/>
       <c r="AB85" s="41"/>
       <c r="AI85" s="41"/>
     </row>
-    <row r="86" spans="1:64" ht="12.5">
+    <row r="86" spans="1:65" ht="12.5">
       <c r="K86" s="38"/>
       <c r="L86" s="38"/>
       <c r="AB86" s="41"/>
       <c r="AI86" s="41"/>
     </row>
-    <row r="87" spans="1:64" ht="12.5">
+    <row r="87" spans="1:65" ht="12.5">
       <c r="K87" s="38"/>
       <c r="L87" s="38"/>
       <c r="AB87" s="41"/>
       <c r="AI87" s="41"/>
     </row>
-    <row r="88" spans="1:64" ht="12.5">
+    <row r="88" spans="1:65" ht="12.5">
       <c r="K88" s="38"/>
       <c r="L88" s="38"/>
       <c r="AB88" s="41"/>
       <c r="AI88" s="41"/>
     </row>
-    <row r="89" spans="1:64" ht="12.5">
+    <row r="89" spans="1:65" ht="12.5">
       <c r="K89" s="38"/>
       <c r="L89" s="38"/>
       <c r="AB89" s="41"/>
       <c r="AI89" s="41"/>
     </row>
-    <row r="90" spans="1:64" ht="12.5">
+    <row r="90" spans="1:65" ht="12.5">
       <c r="K90" s="38"/>
       <c r="L90" s="38"/>
       <c r="AB90" s="41"/>
       <c r="AI90" s="41"/>
     </row>
-    <row r="91" spans="1:64" ht="12.5">
+    <row r="91" spans="1:65" ht="12.5">
       <c r="K91" s="38"/>
       <c r="L91" s="38"/>
       <c r="AB91" s="41"/>
       <c r="AI91" s="41"/>
     </row>
-    <row r="92" spans="1:64" ht="12.5">
+    <row r="92" spans="1:65" ht="12.5">
       <c r="K92" s="38"/>
       <c r="L92" s="38"/>
       <c r="AB92" s="41"/>
       <c r="AI92" s="41"/>
     </row>
-    <row r="93" spans="1:64" ht="12.5">
+    <row r="93" spans="1:65" ht="12.5">
       <c r="K93" s="38"/>
       <c r="L93" s="38"/>
       <c r="AB93" s="41"/>
       <c r="AI93" s="41"/>
     </row>
-    <row r="94" spans="1:64" ht="12.5">
+    <row r="94" spans="1:65" ht="12.5">
       <c r="K94" s="38"/>
       <c r="L94" s="38"/>
       <c r="AB94" s="41"/>
       <c r="AI94" s="41"/>
     </row>
-    <row r="95" spans="1:64" ht="12.5">
+    <row r="95" spans="1:65" ht="12.5">
       <c r="K95" s="38"/>
       <c r="L95" s="38"/>
       <c r="AB95" s="41"/>
       <c r="AI95" s="41"/>
     </row>
-    <row r="96" spans="1:64" ht="12.5">
+    <row r="96" spans="1:65" ht="12.5">
       <c r="K96" s="38"/>
       <c r="L96" s="38"/>
       <c r="AB96" s="41"/>
@@ -57064,7 +57341,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:AG131"/>
+  <dimension ref="A1:AH131"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="22.1796875" customWidth="1"/>
@@ -57080,10 +57357,11 @@
     <col min="29" max="29" width="11.54296875" customWidth="1"/>
     <col min="31" max="31" width="12.26953125" customWidth="1"/>
     <col min="32" max="32" width="7.6328125" customWidth="1"/>
-    <col min="33" max="33" width="7.7265625" customWidth="1"/>
+    <col min="33" max="33" width="10.81640625" customWidth="1"/>
+    <col min="34" max="34" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="13">
+    <row r="1" spans="1:34" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -57183,8 +57461,11 @@
       <c r="AG1" s="43" t="s">
         <v>1529</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
+      <c r="AH1" s="43" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2" s="44" t="s">
         <v>1578</v>
       </c>
@@ -57284,8 +57565,11 @@
       <c r="AG2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:33">
+      <c r="AH2" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3" s="44" t="s">
         <v>1367</v>
       </c>
@@ -57385,8 +57669,11 @@
       <c r="AG3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:33">
+      <c r="AH3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4" s="44" t="s">
         <v>1366</v>
       </c>
@@ -57486,8 +57773,11 @@
       <c r="AG4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:33">
+      <c r="AH4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5" s="44" t="s">
         <v>1776</v>
       </c>
@@ -57587,8 +57877,11 @@
       <c r="AG5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:33">
+      <c r="AH5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6" s="44" t="s">
         <v>1220</v>
       </c>
@@ -57688,8 +57981,11 @@
       <c r="AG6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:33">
+      <c r="AH6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7" s="44" t="s">
         <v>1227</v>
       </c>
@@ -57789,8 +58085,11 @@
       <c r="AG7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:33">
+      <c r="AH7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
       <c r="A8" s="44" t="s">
         <v>1613</v>
       </c>
@@ -57890,8 +58189,11 @@
       <c r="AG8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33">
+      <c r="AH8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34">
       <c r="A9" s="44" t="s">
         <v>1369</v>
       </c>
@@ -57991,8 +58293,11 @@
       <c r="AG9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33">
+      <c r="AH9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34">
       <c r="A10" s="44" t="s">
         <v>1370</v>
       </c>
@@ -58092,10 +58397,13 @@
       <c r="AG10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:33">
+      <c r="AH10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34">
       <c r="A11" s="44" t="s">
-        <v>1142</v>
+        <v>1458</v>
       </c>
       <c r="B11" s="44" t="s">
         <v>1368</v>
@@ -58179,7 +58487,7 @@
         <v>11</v>
       </c>
       <c r="AC11" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="AD11" t="s">
         <v>36</v>
@@ -58193,10 +58501,13 @@
       <c r="AG11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:33">
+      <c r="AH11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34">
       <c r="A12" s="44" t="s">
-        <v>1143</v>
+        <v>1459</v>
       </c>
       <c r="B12" s="44" t="s">
         <v>1368</v>
@@ -58280,7 +58591,7 @@
         <v>11</v>
       </c>
       <c r="AC12" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="AD12" t="s">
         <v>36</v>
@@ -58294,10 +58605,13 @@
       <c r="AG12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:33">
+      <c r="AH12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34">
       <c r="A13" s="44" t="s">
-        <v>1458</v>
+        <v>1507</v>
       </c>
       <c r="B13" s="44" t="s">
         <v>1368</v>
@@ -58381,7 +58695,7 @@
         <v>11</v>
       </c>
       <c r="AC13" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="AD13" t="s">
         <v>36</v>
@@ -58395,10 +58709,13 @@
       <c r="AG13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33">
+      <c r="AH13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34">
       <c r="A14" s="44" t="s">
-        <v>1459</v>
+        <v>1508</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>1368</v>
@@ -58482,7 +58799,7 @@
         <v>11</v>
       </c>
       <c r="AC14" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="AD14" t="s">
         <v>36</v>
@@ -58496,13 +58813,16 @@
       <c r="AG14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33">
+      <c r="AH14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34">
       <c r="A15" s="44" t="s">
-        <v>1507</v>
+        <v>1617</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -58523,7 +58843,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -58538,7 +58858,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -58565,7 +58885,7 @@
         <v>10</v>
       </c>
       <c r="W15" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="X15">
         <v>0</v>
@@ -58577,13 +58897,13 @@
         <v>1182</v>
       </c>
       <c r="AA15" t="s">
-        <v>36</v>
+        <v>1616</v>
       </c>
       <c r="AB15">
         <v>11</v>
       </c>
       <c r="AC15" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="AD15" t="s">
         <v>36</v>
@@ -58597,10 +58917,13 @@
       <c r="AG15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33">
+      <c r="AH15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34">
       <c r="A16" s="44" t="s">
-        <v>1508</v>
+        <v>1625</v>
       </c>
       <c r="B16" s="44" t="s">
         <v>1368</v>
@@ -58684,7 +59007,7 @@
         <v>11</v>
       </c>
       <c r="AC16" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="AD16" t="s">
         <v>36</v>
@@ -58698,13 +59021,16 @@
       <c r="AG16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:33">
+      <c r="AH16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34">
       <c r="A17" s="44" t="s">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>818</v>
+        <v>1368</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -58725,7 +59051,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -58740,7 +59066,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -58767,7 +59093,7 @@
         <v>10</v>
       </c>
       <c r="W17" s="44" t="s">
-        <v>818</v>
+        <v>1368</v>
       </c>
       <c r="X17">
         <v>0</v>
@@ -58779,13 +59105,13 @@
         <v>1182</v>
       </c>
       <c r="AA17" t="s">
-        <v>1616</v>
+        <v>36</v>
       </c>
       <c r="AB17">
         <v>11</v>
       </c>
       <c r="AC17" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="AD17" t="s">
         <v>36</v>
@@ -58799,10 +59125,13 @@
       <c r="AG17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:33">
+      <c r="AH17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34">
       <c r="A18" s="44" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="B18" s="44" t="s">
         <v>1368</v>
@@ -58886,7 +59215,7 @@
         <v>11</v>
       </c>
       <c r="AC18" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="AD18" t="s">
         <v>36</v>
@@ -58900,10 +59229,13 @@
       <c r="AG18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:33">
+      <c r="AH18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34">
       <c r="A19" s="44" t="s">
-        <v>1626</v>
+        <v>1720</v>
       </c>
       <c r="B19" s="44" t="s">
         <v>1368</v>
@@ -58987,7 +59319,7 @@
         <v>11</v>
       </c>
       <c r="AC19" t="s">
-        <v>1673</v>
+        <v>1658</v>
       </c>
       <c r="AD19" t="s">
         <v>36</v>
@@ -59001,10 +59333,13 @@
       <c r="AG19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:33">
+      <c r="AH19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20" s="44" t="s">
-        <v>1627</v>
+        <v>1721</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>1368</v>
@@ -59088,7 +59423,7 @@
         <v>11</v>
       </c>
       <c r="AC20" t="s">
-        <v>1674</v>
+        <v>1658</v>
       </c>
       <c r="AD20" t="s">
         <v>36</v>
@@ -59102,10 +59437,13 @@
       <c r="AG20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:33">
+      <c r="AH20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34">
       <c r="A21" s="44" t="s">
-        <v>1146</v>
+        <v>1728</v>
       </c>
       <c r="B21" s="44" t="s">
         <v>1368</v>
@@ -59203,10 +59541,13 @@
       <c r="AG21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:33">
+      <c r="AH21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34">
       <c r="A22" s="44" t="s">
-        <v>1719</v>
+        <v>1729</v>
       </c>
       <c r="B22" s="44" t="s">
         <v>1368</v>
@@ -59290,7 +59631,7 @@
         <v>11</v>
       </c>
       <c r="AC22" t="s">
-        <v>1658</v>
+        <v>1559</v>
       </c>
       <c r="AD22" t="s">
         <v>36</v>
@@ -59304,10 +59645,13 @@
       <c r="AG22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:33">
+      <c r="AH22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23" s="44" t="s">
-        <v>1720</v>
+        <v>1747</v>
       </c>
       <c r="B23" s="44" t="s">
         <v>1368</v>
@@ -59405,13 +59749,16 @@
       <c r="AG23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:33">
+      <c r="AH23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34">
       <c r="A24" s="44" t="s">
-        <v>1721</v>
+        <v>1777</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>1368</v>
+        <v>1803</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -59420,7 +59767,7 @@
         <v>36</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>36</v>
+        <v>1469</v>
       </c>
       <c r="F24" s="44">
         <v>0</v>
@@ -59492,7 +59839,7 @@
         <v>11</v>
       </c>
       <c r="AC24" t="s">
-        <v>1658</v>
+        <v>896</v>
       </c>
       <c r="AD24" t="s">
         <v>36</v>
@@ -59506,13 +59853,16 @@
       <c r="AG24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:33">
+      <c r="AH24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34">
       <c r="A25" s="44" t="s">
-        <v>1728</v>
+        <v>1778</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>1368</v>
+        <v>1803</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -59521,7 +59871,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>36</v>
+        <v>1805</v>
       </c>
       <c r="F25" s="44">
         <v>0</v>
@@ -59593,7 +59943,7 @@
         <v>11</v>
       </c>
       <c r="AC25" t="s">
-        <v>1658</v>
+        <v>896</v>
       </c>
       <c r="AD25" t="s">
         <v>36</v>
@@ -59607,13 +59957,16 @@
       <c r="AG25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:33">
+      <c r="AH25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26" s="44" t="s">
-        <v>1729</v>
+        <v>238</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>1368</v>
+        <v>1800</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -59649,7 +60002,7 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -59676,7 +60029,7 @@
         <v>10</v>
       </c>
       <c r="W26" s="44" t="s">
-        <v>1368</v>
+        <v>1800</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -59694,7 +60047,7 @@
         <v>11</v>
       </c>
       <c r="AC26" t="s">
-        <v>1559</v>
+        <v>1671</v>
       </c>
       <c r="AD26" t="s">
         <v>36</v>
@@ -59708,13 +60061,16 @@
       <c r="AG26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:33">
+      <c r="AH26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34">
       <c r="A27" s="44" t="s">
-        <v>1740</v>
+        <v>1801</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>1368</v>
+        <v>1802</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -59735,7 +60091,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -59744,7 +60100,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -59777,7 +60133,7 @@
         <v>10</v>
       </c>
       <c r="W27" s="44" t="s">
-        <v>1368</v>
+        <v>1800</v>
       </c>
       <c r="X27">
         <v>0</v>
@@ -59795,7 +60151,7 @@
         <v>11</v>
       </c>
       <c r="AC27" t="s">
-        <v>1658</v>
+        <v>1671</v>
       </c>
       <c r="AD27" t="s">
         <v>36</v>
@@ -59809,13 +60165,16 @@
       <c r="AG27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:33">
+      <c r="AH27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34">
       <c r="A28" s="44" t="s">
-        <v>959</v>
+        <v>1808</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>1368</v>
+        <v>1803</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -59824,7 +60183,7 @@
         <v>36</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>36</v>
+        <v>1807</v>
       </c>
       <c r="F28" s="44">
         <v>0</v>
@@ -59896,7 +60255,7 @@
         <v>11</v>
       </c>
       <c r="AC28" t="s">
-        <v>1658</v>
+        <v>896</v>
       </c>
       <c r="AD28" t="s">
         <v>36</v>
@@ -59910,114 +60269,36 @@
       <c r="AG28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:33">
-      <c r="A29" s="44" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B29" s="44" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" s="44">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>10</v>
-      </c>
-      <c r="W29" s="44" t="s">
-        <v>1368</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB29">
-        <v>11</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>1658</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE29">
-        <v>5</v>
-      </c>
+      <c r="AH28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" ht="14">
+      <c r="A29" s="55" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="W29" s="44"/>
+      <c r="Z29" s="44"/>
       <c r="AF29">
         <v>0</v>
       </c>
       <c r="AG29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:33">
+      <c r="AH29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34">
       <c r="A30" s="44" t="s">
-        <v>1777</v>
+        <v>1875</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>1803</v>
+        <v>1876</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -60026,10 +60307,10 @@
         <v>36</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>1469</v>
+        <v>36</v>
       </c>
       <c r="F30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -60038,7 +60319,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -60098,13 +60379,13 @@
         <v>11</v>
       </c>
       <c r="AC30" t="s">
-        <v>896</v>
+        <v>1663</v>
       </c>
       <c r="AD30" t="s">
         <v>36</v>
       </c>
       <c r="AE30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF30">
         <v>0</v>
@@ -60112,13 +60393,16 @@
       <c r="AG30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:33">
+      <c r="AH30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34">
       <c r="A31" s="44" t="s">
-        <v>1778</v>
+        <v>1877</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>1803</v>
+        <v>1876</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -60127,10 +60411,10 @@
         <v>36</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>1805</v>
+        <v>36</v>
       </c>
       <c r="F31" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -60154,7 +60438,7 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -60199,13 +60483,13 @@
         <v>11</v>
       </c>
       <c r="AC31" t="s">
-        <v>896</v>
+        <v>1663</v>
       </c>
       <c r="AD31" t="s">
         <v>36</v>
       </c>
       <c r="AE31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -60213,13 +60497,16 @@
       <c r="AG31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:33">
+      <c r="AH31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34">
       <c r="A32" s="44" t="s">
-        <v>238</v>
+        <v>1878</v>
       </c>
       <c r="B32" s="44" t="s">
-        <v>1800</v>
+        <v>1876</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -60231,7 +60518,7 @@
         <v>36</v>
       </c>
       <c r="F32" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -60249,13 +60536,13 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -60282,7 +60569,7 @@
         <v>10</v>
       </c>
       <c r="W32" s="44" t="s">
-        <v>1800</v>
+        <v>1368</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -60300,13 +60587,13 @@
         <v>11</v>
       </c>
       <c r="AC32" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="AD32" t="s">
         <v>36</v>
       </c>
       <c r="AE32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -60314,13 +60601,16 @@
       <c r="AG32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:33">
+      <c r="AH32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34">
       <c r="A33" s="44" t="s">
-        <v>1801</v>
+        <v>2050</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>1802</v>
+        <v>1876</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -60332,7 +60622,7 @@
         <v>36</v>
       </c>
       <c r="F33" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -60341,7 +60631,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -60350,7 +60640,7 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -60383,7 +60673,7 @@
         <v>10</v>
       </c>
       <c r="W33" s="44" t="s">
-        <v>1800</v>
+        <v>1368</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -60401,27 +60691,30 @@
         <v>11</v>
       </c>
       <c r="AC33" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="AD33" t="s">
         <v>36</v>
       </c>
       <c r="AE33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33">
+        <v>10</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34">
       <c r="A34" s="44" t="s">
-        <v>1808</v>
+        <v>2049</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>1803</v>
+        <v>1876</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -60430,10 +60723,10 @@
         <v>36</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>1807</v>
+        <v>36</v>
       </c>
       <c r="F34" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -60502,41 +60795,131 @@
         <v>11</v>
       </c>
       <c r="AC34" t="s">
-        <v>896</v>
+        <v>1663</v>
       </c>
       <c r="AD34" t="s">
         <v>36</v>
       </c>
       <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
         <v>5</v>
       </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
       <c r="AG34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:33" ht="14">
-      <c r="A35" s="55" t="s">
-        <v>1953</v>
-      </c>
-      <c r="B35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="W35" s="44"/>
-      <c r="Z35" s="44"/>
+      <c r="AH34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34">
+      <c r="A35" s="44" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="44">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>40</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>10</v>
+      </c>
+      <c r="W35" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB35">
+        <v>11</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
       <c r="AF35">
         <v>0</v>
       </c>
       <c r="AG35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:33">
+      <c r="AH35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34">
       <c r="A36" s="44" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="B36" s="44" t="s">
         <v>1876</v>
@@ -60560,10 +60943,10 @@
         <v>0</v>
       </c>
       <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
         <v>20</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -60634,100 +61017,13 @@
       <c r="AG36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:33">
-      <c r="A37" s="44" t="s">
-        <v>1877</v>
-      </c>
-      <c r="B37" s="44" t="s">
-        <v>1876</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37" s="44">
-        <v>1</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>50</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>10</v>
-      </c>
-      <c r="W37" s="44" t="s">
-        <v>1368</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="44" t="s">
-        <v>1182</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB37">
-        <v>11</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
+      <c r="AH36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" ht="14">
+      <c r="A37" s="55" t="s">
+        <v>1954</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -60735,13 +61031,16 @@
       <c r="AG37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:33">
+      <c r="AH37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34">
       <c r="A38" s="44" t="s">
-        <v>1878</v>
+        <v>1948</v>
       </c>
       <c r="B38" s="44" t="s">
-        <v>1876</v>
+        <v>818</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -60762,7 +61061,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -60771,10 +61070,10 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -60804,7 +61103,7 @@
         <v>10</v>
       </c>
       <c r="W38" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="X38">
         <v>0</v>
@@ -60828,7 +61127,7 @@
         <v>36</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -60836,13 +61135,16 @@
       <c r="AG38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:33">
+      <c r="AH38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34">
       <c r="A39" s="44" t="s">
-        <v>2050</v>
+        <v>1949</v>
       </c>
       <c r="B39" s="44" t="s">
-        <v>1876</v>
+        <v>818</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -60863,7 +61165,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -60905,7 +61207,7 @@
         <v>10</v>
       </c>
       <c r="W39" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -60929,21 +61231,24 @@
         <v>36</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF39">
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:33">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34">
       <c r="A40" s="44" t="s">
-        <v>2049</v>
+        <v>1950</v>
       </c>
       <c r="B40" s="44" t="s">
-        <v>1876</v>
+        <v>818</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -60964,7 +61269,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -61006,7 +61311,7 @@
         <v>10</v>
       </c>
       <c r="W40" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -61030,21 +61335,24 @@
         <v>36</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:33">
+      <c r="AH40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34">
       <c r="A41" s="44" t="s">
-        <v>2048</v>
+        <v>1951</v>
       </c>
       <c r="B41" s="44" t="s">
-        <v>1876</v>
+        <v>818</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -61065,7 +61373,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -61083,7 +61391,7 @@
         <v>0</v>
       </c>
       <c r="O41">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -61107,7 +61415,7 @@
         <v>10</v>
       </c>
       <c r="W41" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="X41">
         <v>0</v>
@@ -61131,7 +61439,7 @@
         <v>36</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -61139,13 +61447,16 @@
       <c r="AG41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:33">
+      <c r="AH41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:34">
       <c r="A42" s="44" t="s">
-        <v>1879</v>
+        <v>1952</v>
       </c>
       <c r="B42" s="44" t="s">
-        <v>1876</v>
+        <v>818</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -61166,10 +61477,10 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -61208,7 +61519,7 @@
         <v>10</v>
       </c>
       <c r="W42" s="44" t="s">
-        <v>1368</v>
+        <v>818</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -61232,18 +61543,21 @@
         <v>36</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:33" ht="14">
+      <c r="AH42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:34" ht="14">
       <c r="A43" s="55" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -61251,13 +61565,16 @@
       <c r="AG43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:33">
+      <c r="AH43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34">
       <c r="A44" s="44" t="s">
-        <v>1948</v>
+        <v>1956</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -61320,7 +61637,7 @@
         <v>10</v>
       </c>
       <c r="W44" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -61352,13 +61669,16 @@
       <c r="AG44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:33">
+      <c r="AH44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:34">
       <c r="A45" s="44" t="s">
-        <v>1949</v>
+        <v>1957</v>
       </c>
       <c r="B45" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -61421,7 +61741,7 @@
         <v>10</v>
       </c>
       <c r="W45" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="X45">
         <v>0</v>
@@ -61453,13 +61773,16 @@
       <c r="AG45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:33">
+      <c r="AH45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:34">
       <c r="A46" s="44" t="s">
-        <v>1950</v>
+        <v>1958</v>
       </c>
       <c r="B46" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -61522,7 +61845,7 @@
         <v>10</v>
       </c>
       <c r="W46" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -61554,13 +61877,16 @@
       <c r="AG46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:33">
+      <c r="AH46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34">
       <c r="A47" s="44" t="s">
-        <v>1951</v>
+        <v>1959</v>
       </c>
       <c r="B47" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -61623,7 +61949,7 @@
         <v>10</v>
       </c>
       <c r="W47" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -61655,13 +61981,16 @@
       <c r="AG47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:33">
+      <c r="AH47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:34">
       <c r="A48" s="44" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="B48" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -61724,7 +62053,7 @@
         <v>10</v>
       </c>
       <c r="W48" s="44" t="s">
-        <v>818</v>
+        <v>1802</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -61751,15 +62080,18 @@
         <v>5</v>
       </c>
       <c r="AF48">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AG48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:33" ht="14">
+      <c r="AH48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:34" ht="14">
       <c r="A49" s="55" t="s">
-        <v>1955</v>
+        <v>1961</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -61767,13 +62099,16 @@
       <c r="AG49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:33">
-      <c r="A50" s="44" t="s">
-        <v>1956</v>
+      <c r="AH49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:34">
+      <c r="A50" t="s">
+        <v>1962</v>
       </c>
       <c r="B50" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -61836,7 +62171,7 @@
         <v>10</v>
       </c>
       <c r="W50" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -61868,13 +62203,16 @@
       <c r="AG50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:33">
-      <c r="A51" s="44" t="s">
-        <v>1957</v>
+      <c r="AH50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:34">
+      <c r="A51" t="s">
+        <v>1963</v>
       </c>
       <c r="B51" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -61937,7 +62275,7 @@
         <v>10</v>
       </c>
       <c r="W51" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="X51">
         <v>0</v>
@@ -61969,13 +62307,16 @@
       <c r="AG51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:33">
-      <c r="A52" s="44" t="s">
-        <v>1958</v>
+      <c r="AH51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:34">
+      <c r="A52" s="60" t="s">
+        <v>1964</v>
       </c>
       <c r="B52" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -62038,7 +62379,7 @@
         <v>10</v>
       </c>
       <c r="W52" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="X52">
         <v>0</v>
@@ -62070,13 +62411,16 @@
       <c r="AG52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:33">
-      <c r="A53" s="44" t="s">
-        <v>1959</v>
+      <c r="AH52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:34">
+      <c r="A53" t="s">
+        <v>1965</v>
       </c>
       <c r="B53" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -62139,7 +62483,7 @@
         <v>10</v>
       </c>
       <c r="W53" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -62171,13 +62515,16 @@
       <c r="AG53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:33">
-      <c r="A54" s="44" t="s">
-        <v>1960</v>
+      <c r="AH53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:34">
+      <c r="A54" t="s">
+        <v>1966</v>
       </c>
       <c r="B54" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -62240,7 +62587,7 @@
         <v>10</v>
       </c>
       <c r="W54" s="44" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="X54">
         <v>0</v>
@@ -62272,10 +62619,13 @@
       <c r="AG54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:33" ht="14">
+      <c r="AH54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:34" ht="14">
       <c r="A55" s="55" t="s">
-        <v>1961</v>
+        <v>1967</v>
       </c>
       <c r="AF55">
         <v>0</v>
@@ -62283,13 +62633,16 @@
       <c r="AG55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:33">
+      <c r="AH55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:34">
       <c r="A56" t="s">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="B56" s="44" t="s">
-        <v>1800</v>
+        <v>846</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -62352,7 +62705,7 @@
         <v>10</v>
       </c>
       <c r="W56" s="44" t="s">
-        <v>1800</v>
+        <v>1973</v>
       </c>
       <c r="X56">
         <v>0</v>
@@ -62384,13 +62737,16 @@
       <c r="AG56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:33">
+      <c r="AH56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:34">
       <c r="A57" t="s">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="B57" s="44" t="s">
-        <v>1800</v>
+        <v>846</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -62453,7 +62809,7 @@
         <v>10</v>
       </c>
       <c r="W57" s="44" t="s">
-        <v>1800</v>
+        <v>1973</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -62485,13 +62841,16 @@
       <c r="AG57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:33">
-      <c r="A58" s="60" t="s">
-        <v>1964</v>
+      <c r="AH57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:34">
+      <c r="A58" t="s">
+        <v>1970</v>
       </c>
       <c r="B58" s="44" t="s">
-        <v>1800</v>
+        <v>846</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -62554,7 +62913,7 @@
         <v>10</v>
       </c>
       <c r="W58" s="44" t="s">
-        <v>1800</v>
+        <v>1973</v>
       </c>
       <c r="X58">
         <v>0</v>
@@ -62586,13 +62945,16 @@
       <c r="AG58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:33">
+      <c r="AH58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:34">
       <c r="A59" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
       <c r="B59" s="44" t="s">
-        <v>1800</v>
+        <v>846</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -62655,7 +63017,7 @@
         <v>10</v>
       </c>
       <c r="W59" s="44" t="s">
-        <v>1800</v>
+        <v>1973</v>
       </c>
       <c r="X59">
         <v>0</v>
@@ -62687,13 +63049,16 @@
       <c r="AG59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:33">
+      <c r="AH59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:34">
       <c r="A60" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="B60" s="44" t="s">
-        <v>1800</v>
+        <v>846</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -62756,7 +63121,7 @@
         <v>10</v>
       </c>
       <c r="W60" s="44" t="s">
-        <v>1800</v>
+        <v>1973</v>
       </c>
       <c r="X60">
         <v>0</v>
@@ -62788,10 +63153,13 @@
       <c r="AG60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:33" ht="14">
+      <c r="AH60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:34" ht="14">
       <c r="A61" s="55" t="s">
-        <v>1967</v>
+        <v>1974</v>
       </c>
       <c r="AF61">
         <v>0</v>
@@ -62799,13 +63167,16 @@
       <c r="AG61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:33">
+      <c r="AH61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:34">
       <c r="A62" t="s">
-        <v>1968</v>
+        <v>1975</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>846</v>
+        <v>1987</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -62868,7 +63239,7 @@
         <v>10</v>
       </c>
       <c r="W62" s="44" t="s">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -62900,13 +63271,16 @@
       <c r="AG62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:33">
+      <c r="AH62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:34">
       <c r="A63" t="s">
-        <v>1969</v>
+        <v>1976</v>
       </c>
       <c r="B63" s="44" t="s">
-        <v>846</v>
+        <v>1987</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -62969,7 +63343,7 @@
         <v>10</v>
       </c>
       <c r="W63" s="44" t="s">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="X63">
         <v>0</v>
@@ -63001,13 +63375,16 @@
       <c r="AG63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:33">
+      <c r="AH63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:34">
       <c r="A64" t="s">
-        <v>1970</v>
+        <v>1977</v>
       </c>
       <c r="B64" s="44" t="s">
-        <v>846</v>
+        <v>1987</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -63070,7 +63447,7 @@
         <v>10</v>
       </c>
       <c r="W64" s="44" t="s">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="X64">
         <v>0</v>
@@ -63102,13 +63479,16 @@
       <c r="AG64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:33">
+      <c r="AH64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:34">
       <c r="A65" t="s">
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="B65" s="44" t="s">
-        <v>846</v>
+        <v>1987</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -63171,7 +63551,7 @@
         <v>10</v>
       </c>
       <c r="W65" s="44" t="s">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="X65">
         <v>0</v>
@@ -63203,13 +63583,16 @@
       <c r="AG65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:33">
+      <c r="AH65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:34">
       <c r="A66" t="s">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="B66" s="44" t="s">
-        <v>846</v>
+        <v>1987</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -63272,7 +63655,7 @@
         <v>10</v>
       </c>
       <c r="W66" s="44" t="s">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="X66">
         <v>0</v>
@@ -63304,24 +63687,26 @@
       <c r="AG66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:33" ht="14">
+      <c r="AH66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:34" ht="14">
       <c r="A67" s="55" t="s">
-        <v>1974</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:33">
+        <v>1980</v>
+      </c>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:34">
       <c r="A68" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="B68" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -63384,7 +63769,7 @@
         <v>10</v>
       </c>
       <c r="W68" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="X68">
         <v>0</v>
@@ -63416,13 +63801,16 @@
       <c r="AG68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:33">
+      <c r="AH68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:34">
       <c r="A69" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="B69" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -63485,7 +63873,7 @@
         <v>10</v>
       </c>
       <c r="W69" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -63517,13 +63905,16 @@
       <c r="AG69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:33">
+      <c r="AH69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:34">
       <c r="A70" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
       <c r="B70" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -63586,7 +63977,7 @@
         <v>10</v>
       </c>
       <c r="W70" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="X70">
         <v>0</v>
@@ -63618,13 +64009,16 @@
       <c r="AG70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:33">
+      <c r="AH70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:34">
       <c r="A71" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="B71" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -63687,7 +64081,7 @@
         <v>10</v>
       </c>
       <c r="W71" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="X71">
         <v>0</v>
@@ -63719,13 +64113,16 @@
       <c r="AG71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:33">
+      <c r="AH71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:34">
       <c r="A72" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
       <c r="B72" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -63788,7 +64185,7 @@
         <v>10</v>
       </c>
       <c r="W72" s="44" t="s">
-        <v>1987</v>
+        <v>833</v>
       </c>
       <c r="X72">
         <v>0</v>
@@ -63820,20 +64217,26 @@
       <c r="AG72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:33" ht="14">
+      <c r="AH72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:34" ht="14">
       <c r="A73" s="55" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="AF73" s="3"/>
       <c r="AG73" s="3"/>
-    </row>
-    <row r="74" spans="1:33">
+      <c r="AH73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:34">
       <c r="A74" t="s">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="B74" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -63896,7 +64299,7 @@
         <v>10</v>
       </c>
       <c r="W74" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="X74">
         <v>0</v>
@@ -63922,19 +64325,22 @@
       <c r="AE74">
         <v>5</v>
       </c>
-      <c r="AF74">
-        <v>0</v>
-      </c>
-      <c r="AG74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:33">
+      <c r="AF74" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG74" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:34">
       <c r="A75" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="B75" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -63997,7 +64403,7 @@
         <v>10</v>
       </c>
       <c r="W75" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="X75">
         <v>0</v>
@@ -64023,19 +64429,22 @@
       <c r="AE75">
         <v>5</v>
       </c>
-      <c r="AF75">
-        <v>0</v>
-      </c>
-      <c r="AG75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:33">
+      <c r="AF75" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG75" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:34">
       <c r="A76" t="s">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="B76" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -64098,7 +64507,7 @@
         <v>10</v>
       </c>
       <c r="W76" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="X76">
         <v>0</v>
@@ -64124,19 +64533,22 @@
       <c r="AE76">
         <v>5</v>
       </c>
-      <c r="AF76">
-        <v>0</v>
-      </c>
-      <c r="AG76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:33">
+      <c r="AF76" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:34">
       <c r="A77" t="s">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="B77" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -64199,7 +64611,7 @@
         <v>10</v>
       </c>
       <c r="W77" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="X77">
         <v>0</v>
@@ -64225,19 +64637,22 @@
       <c r="AE77">
         <v>5</v>
       </c>
-      <c r="AF77">
-        <v>0</v>
-      </c>
-      <c r="AG77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:33">
+      <c r="AF77" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG77" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34">
       <c r="A78" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="B78" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -64300,7 +64715,7 @@
         <v>10</v>
       </c>
       <c r="W78" s="44" t="s">
-        <v>833</v>
+        <v>1079</v>
       </c>
       <c r="X78">
         <v>0</v>
@@ -64326,32 +64741,38 @@
       <c r="AE78">
         <v>5</v>
       </c>
-      <c r="AF78">
-        <v>0</v>
-      </c>
-      <c r="AG78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:33" ht="14">
+      <c r="AF78" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG78" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:34" ht="14">
       <c r="A79" s="55" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="AF79" s="3"/>
       <c r="AG79" s="3"/>
-    </row>
-    <row r="80" spans="1:33">
+      <c r="AH79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34">
       <c r="A80" t="s">
-        <v>1989</v>
+        <v>1994</v>
       </c>
       <c r="B80" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80" s="44" t="s">
-        <v>36</v>
+        <v>2040</v>
       </c>
       <c r="E80" s="44" t="s">
         <v>36</v>
@@ -64408,7 +64829,7 @@
         <v>10</v>
       </c>
       <c r="W80" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -64434,15 +64855,22 @@
       <c r="AE80">
         <v>5</v>
       </c>
-      <c r="AF80" s="3"/>
-      <c r="AG80" s="3"/>
-    </row>
-    <row r="81" spans="1:33">
+      <c r="AF80" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG80" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:34">
       <c r="A81" t="s">
-        <v>1990</v>
+        <v>1995</v>
       </c>
       <c r="B81" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -64505,7 +64933,7 @@
         <v>10</v>
       </c>
       <c r="W81" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -64531,15 +64959,22 @@
       <c r="AE81">
         <v>5</v>
       </c>
-      <c r="AF81" s="3"/>
-      <c r="AG81" s="3"/>
-    </row>
-    <row r="82" spans="1:33">
+      <c r="AF81" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:34">
       <c r="A82" t="s">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="B82" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -64602,7 +65037,7 @@
         <v>10</v>
       </c>
       <c r="W82" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -64628,15 +65063,22 @@
       <c r="AE82">
         <v>5</v>
       </c>
-      <c r="AF82" s="3"/>
-      <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="1:33">
+      <c r="AF82" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG82" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:34">
       <c r="A83" t="s">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="B83" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -64699,7 +65141,7 @@
         <v>10</v>
       </c>
       <c r="W83" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -64725,15 +65167,22 @@
       <c r="AE83">
         <v>5</v>
       </c>
-      <c r="AF83" s="3"/>
-      <c r="AG83" s="3"/>
-    </row>
-    <row r="84" spans="1:33">
+      <c r="AF83" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:34">
       <c r="A84" t="s">
-        <v>1993</v>
+        <v>1998</v>
       </c>
       <c r="B84" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -64796,7 +65245,7 @@
         <v>10</v>
       </c>
       <c r="W84" s="44" t="s">
-        <v>1079</v>
+        <v>821</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -64822,34 +65271,44 @@
       <c r="AE84">
         <v>5</v>
       </c>
-      <c r="AF84" s="3"/>
-      <c r="AG84" s="3"/>
-    </row>
-    <row r="85" spans="1:33" ht="14">
+      <c r="AF84" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AG84" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AH84" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:34" ht="14">
       <c r="A85" s="55" t="s">
-        <v>1988</v>
+        <v>2056</v>
       </c>
       <c r="AF85" s="3"/>
       <c r="AG85" s="3"/>
-    </row>
-    <row r="86" spans="1:33">
-      <c r="A86" t="s">
-        <v>1994</v>
+      <c r="AH85" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:34" ht="13">
+      <c r="A86" s="1" t="s">
+        <v>2057</v>
       </c>
       <c r="B86" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86" s="44" t="s">
-        <v>2040</v>
+        <v>36</v>
       </c>
       <c r="E86" s="44" t="s">
         <v>36</v>
       </c>
       <c r="F86" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -64858,7 +65317,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -64900,7 +65359,7 @@
         <v>10</v>
       </c>
       <c r="W86" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -64918,7 +65377,7 @@
         <v>11</v>
       </c>
       <c r="AC86" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="AD86" t="s">
         <v>36</v>
@@ -64926,18 +65385,25 @@
       <c r="AE86">
         <v>5</v>
       </c>
-      <c r="AF86" s="3"/>
-      <c r="AG86" s="3"/>
-    </row>
-    <row r="87" spans="1:33">
-      <c r="A87" t="s">
-        <v>1995</v>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:34" ht="13">
+      <c r="A87" s="1" t="s">
+        <v>2058</v>
       </c>
       <c r="B87" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" s="44" t="s">
         <v>36</v>
@@ -64946,7 +65412,7 @@
         <v>36</v>
       </c>
       <c r="F87" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -64955,7 +65421,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -64997,7 +65463,7 @@
         <v>10</v>
       </c>
       <c r="W87" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="X87">
         <v>0</v>
@@ -65015,7 +65481,7 @@
         <v>11</v>
       </c>
       <c r="AC87" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="AD87" t="s">
         <v>36</v>
@@ -65023,18 +65489,25 @@
       <c r="AE87">
         <v>5</v>
       </c>
-      <c r="AF87" s="3"/>
-      <c r="AG87" s="3"/>
-    </row>
-    <row r="88" spans="1:33">
-      <c r="A88" t="s">
-        <v>1996</v>
+      <c r="AF87">
+        <v>0</v>
+      </c>
+      <c r="AG87">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:34" ht="13">
+      <c r="A88" s="1" t="s">
+        <v>2059</v>
       </c>
       <c r="B88" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" s="44" t="s">
         <v>36</v>
@@ -65043,7 +65516,7 @@
         <v>36</v>
       </c>
       <c r="F88" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -65052,7 +65525,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -65094,7 +65567,7 @@
         <v>10</v>
       </c>
       <c r="W88" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="X88">
         <v>0</v>
@@ -65112,7 +65585,7 @@
         <v>11</v>
       </c>
       <c r="AC88" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="AD88" t="s">
         <v>36</v>
@@ -65120,18 +65593,25 @@
       <c r="AE88">
         <v>5</v>
       </c>
-      <c r="AF88" s="3"/>
-      <c r="AG88" s="3"/>
-    </row>
-    <row r="89" spans="1:33">
-      <c r="A89" t="s">
-        <v>1997</v>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:34" ht="13">
+      <c r="A89" s="1" t="s">
+        <v>2060</v>
       </c>
       <c r="B89" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D89" s="44" t="s">
         <v>36</v>
@@ -65140,7 +65620,7 @@
         <v>36</v>
       </c>
       <c r="F89" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -65149,7 +65629,7 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -65191,7 +65671,7 @@
         <v>10</v>
       </c>
       <c r="W89" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="X89">
         <v>0</v>
@@ -65209,7 +65689,7 @@
         <v>11</v>
       </c>
       <c r="AC89" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="AD89" t="s">
         <v>36</v>
@@ -65217,18 +65697,25 @@
       <c r="AE89">
         <v>5</v>
       </c>
-      <c r="AF89" s="3"/>
-      <c r="AG89" s="3"/>
-    </row>
-    <row r="90" spans="1:33">
-      <c r="A90" t="s">
-        <v>1998</v>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:34" ht="13">
+      <c r="A90" s="1" t="s">
+        <v>2061</v>
       </c>
       <c r="B90" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D90" s="44" t="s">
         <v>36</v>
@@ -65237,7 +65724,7 @@
         <v>36</v>
       </c>
       <c r="F90" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -65246,7 +65733,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -65288,7 +65775,7 @@
         <v>10</v>
       </c>
       <c r="W90" s="44" t="s">
-        <v>821</v>
+        <v>1368</v>
       </c>
       <c r="X90">
         <v>0</v>
@@ -65306,7 +65793,7 @@
         <v>11</v>
       </c>
       <c r="AC90" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="AD90" t="s">
         <v>36</v>
@@ -65314,25 +65801,129 @@
       <c r="AE90">
         <v>5</v>
       </c>
-      <c r="AF90" s="3"/>
-      <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="1:33" ht="14">
-      <c r="A91" s="55" t="s">
-        <v>2056</v>
-      </c>
-      <c r="AF91" s="3"/>
-      <c r="AG91" s="3"/>
-    </row>
-    <row r="92" spans="1:33" ht="13">
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:34" ht="13">
+      <c r="A91" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B91" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C91">
+        <v>5</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91" s="44">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>10</v>
+      </c>
+      <c r="W91" s="44" t="s">
+        <v>1368</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB91">
+        <v>11</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE91">
+        <v>5</v>
+      </c>
+      <c r="AF91">
+        <v>0</v>
+      </c>
+      <c r="AG91">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="1:34" ht="13">
       <c r="A92" s="1" t="s">
-        <v>2057</v>
+        <v>2063</v>
       </c>
       <c r="B92" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D92" s="44" t="s">
         <v>36</v>
@@ -65424,16 +66015,19 @@
       <c r="AG92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:33" ht="13">
+      <c r="AH92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:34" ht="13">
       <c r="A93" s="1" t="s">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="B93" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D93" s="44" t="s">
         <v>36</v>
@@ -65525,16 +66119,19 @@
       <c r="AG93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:33" ht="13">
+      <c r="AH93" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:34" ht="13">
       <c r="A94" s="1" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="B94" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D94" s="44" t="s">
         <v>36</v>
@@ -65626,16 +66223,19 @@
       <c r="AG94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:33" ht="13">
+      <c r="AH94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:34" ht="13">
       <c r="A95" s="1" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
       <c r="B95" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D95" s="44" t="s">
         <v>36</v>
@@ -65727,16 +66327,19 @@
       <c r="AG95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:33" ht="13">
-      <c r="A96" s="1" t="s">
-        <v>2061</v>
+      <c r="AH95" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:34" ht="14">
+      <c r="A96" s="57" t="s">
+        <v>2067</v>
       </c>
       <c r="B96" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C96">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D96" s="44" t="s">
         <v>36</v>
@@ -65828,16 +66431,19 @@
       <c r="AG96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:33" ht="13">
+      <c r="AH96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:34" ht="13">
       <c r="A97" s="1" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
       <c r="B97" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D97" s="44" t="s">
         <v>36</v>
@@ -65929,16 +66535,19 @@
       <c r="AG97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:33" ht="13">
+      <c r="AH97" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:34" ht="13">
       <c r="A98" s="1" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="B98" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C98">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D98" s="44" t="s">
         <v>36</v>
@@ -66030,16 +66639,19 @@
       <c r="AG98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:33" ht="13">
+      <c r="AH98" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:34" ht="13">
       <c r="A99" s="1" t="s">
-        <v>2064</v>
+        <v>2070</v>
       </c>
       <c r="B99" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D99" s="44" t="s">
         <v>36</v>
@@ -66131,16 +66743,19 @@
       <c r="AG99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:33" ht="13">
+      <c r="AH99" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:34" ht="13">
       <c r="A100" s="1" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="B100" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D100" s="44" t="s">
         <v>36</v>
@@ -66232,16 +66847,19 @@
       <c r="AG100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:33" ht="13">
+      <c r="AH100" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:34" ht="13">
       <c r="A101" s="1" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="B101" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C101">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D101" s="44" t="s">
         <v>36</v>
@@ -66333,16 +66951,19 @@
       <c r="AG101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:33" ht="14">
-      <c r="A102" s="57" t="s">
-        <v>2067</v>
+      <c r="AH101" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:34" ht="13">
+      <c r="A102" s="1" t="s">
+        <v>2073</v>
       </c>
       <c r="B102" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D102" s="44" t="s">
         <v>36</v>
@@ -66434,16 +67055,19 @@
       <c r="AG102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:33" ht="13">
+      <c r="AH102" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:34" ht="13">
       <c r="A103" s="1" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
       <c r="B103" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D103" s="44" t="s">
         <v>36</v>
@@ -66535,16 +67159,19 @@
       <c r="AG103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:33" ht="13">
+      <c r="AH103" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:34" ht="13">
       <c r="A104" s="1" t="s">
-        <v>2069</v>
+        <v>2075</v>
       </c>
       <c r="B104" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D104" s="44" t="s">
         <v>36</v>
@@ -66636,16 +67263,19 @@
       <c r="AG104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:33" ht="13">
+      <c r="AH104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:34" ht="13">
       <c r="A105" s="1" t="s">
-        <v>2070</v>
+        <v>2076</v>
       </c>
       <c r="B105" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C105">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D105" s="44" t="s">
         <v>36</v>
@@ -66737,16 +67367,19 @@
       <c r="AG105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:33" ht="13">
-      <c r="A106" s="1" t="s">
-        <v>2071</v>
+      <c r="AH105" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:34" ht="14">
+      <c r="A106" s="57" t="s">
+        <v>2077</v>
       </c>
       <c r="B106" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C106">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D106" s="44" t="s">
         <v>36</v>
@@ -66838,16 +67471,19 @@
       <c r="AG106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:33" ht="13">
+      <c r="AH106" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:34" ht="13">
       <c r="A107" s="1" t="s">
-        <v>2072</v>
+        <v>2078</v>
       </c>
       <c r="B107" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D107" s="44" t="s">
         <v>36</v>
@@ -66939,16 +67575,19 @@
       <c r="AG107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:33" ht="13">
+      <c r="AH107" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:34" ht="13">
       <c r="A108" s="1" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="B108" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D108" s="44" t="s">
         <v>36</v>
@@ -67040,16 +67679,19 @@
       <c r="AG108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:33" ht="13">
+      <c r="AH108" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:34" ht="13">
       <c r="A109" s="1" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="B109" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D109" s="44" t="s">
         <v>36</v>
@@ -67141,16 +67783,19 @@
       <c r="AG109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:33" ht="13">
+      <c r="AH109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:34" ht="13">
       <c r="A110" s="1" t="s">
-        <v>2075</v>
+        <v>2081</v>
       </c>
       <c r="B110" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D110" s="44" t="s">
         <v>36</v>
@@ -67242,16 +67887,19 @@
       <c r="AG110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:33" ht="13">
+      <c r="AH110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:34" ht="13">
       <c r="A111" s="1" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="B111" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C111">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D111" s="44" t="s">
         <v>36</v>
@@ -67343,16 +67991,19 @@
       <c r="AG111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:33" ht="14">
-      <c r="A112" s="57" t="s">
-        <v>2077</v>
+      <c r="AH111" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:34" ht="13">
+      <c r="A112" s="1" t="s">
+        <v>2083</v>
       </c>
       <c r="B112" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D112" s="44" t="s">
         <v>36</v>
@@ -67444,16 +68095,19 @@
       <c r="AG112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:33" ht="13">
+      <c r="AH112" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="1:34" ht="13">
       <c r="A113" s="1" t="s">
-        <v>2078</v>
+        <v>2084</v>
       </c>
       <c r="B113" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D113" s="44" t="s">
         <v>36</v>
@@ -67545,16 +68199,19 @@
       <c r="AG113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:33" ht="13">
+      <c r="AH113" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:34" ht="13">
       <c r="A114" s="1" t="s">
-        <v>2079</v>
+        <v>2085</v>
       </c>
       <c r="B114" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D114" s="44" t="s">
         <v>36</v>
@@ -67646,16 +68303,19 @@
       <c r="AG114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:33" ht="13">
+      <c r="AH114" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:34" ht="13">
       <c r="A115" s="1" t="s">
-        <v>2080</v>
+        <v>2086</v>
       </c>
       <c r="B115" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D115" s="44" t="s">
         <v>36</v>
@@ -67747,16 +68407,19 @@
       <c r="AG115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:33" ht="13">
-      <c r="A116" s="1" t="s">
-        <v>2081</v>
+      <c r="AH115" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:34" ht="14">
+      <c r="A116" s="57" t="s">
+        <v>2087</v>
       </c>
       <c r="B116" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C116">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D116" s="44" t="s">
         <v>36</v>
@@ -67848,16 +68511,19 @@
       <c r="AG116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:33" ht="13">
+      <c r="AH116" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:34" ht="13">
       <c r="A117" s="1" t="s">
-        <v>2082</v>
+        <v>2088</v>
       </c>
       <c r="B117" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" s="44" t="s">
         <v>36</v>
@@ -67949,16 +68615,19 @@
       <c r="AG117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:33" ht="13">
+      <c r="AH117" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:34" ht="13">
       <c r="A118" s="1" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
       <c r="B118" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C118">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D118" s="44" t="s">
         <v>36</v>
@@ -68050,16 +68719,19 @@
       <c r="AG118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:33" ht="13">
+      <c r="AH118" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:34" ht="13">
       <c r="A119" s="1" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="B119" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D119" s="44" t="s">
         <v>36</v>
@@ -68151,16 +68823,19 @@
       <c r="AG119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:33" ht="13">
+      <c r="AH119" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="120" spans="1:34" ht="13">
       <c r="A120" s="1" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="B120" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C120">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D120" s="44" t="s">
         <v>36</v>
@@ -68252,16 +68927,19 @@
       <c r="AG120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:33" ht="13">
+      <c r="AH120" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="121" spans="1:34" ht="13">
       <c r="A121" s="1" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="B121" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C121">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D121" s="44" t="s">
         <v>36</v>
@@ -68353,16 +69031,19 @@
       <c r="AG121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:33" ht="14">
-      <c r="A122" s="57" t="s">
-        <v>2087</v>
+      <c r="AH121" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="122" spans="1:34" ht="13">
+      <c r="A122" s="1" t="s">
+        <v>2093</v>
       </c>
       <c r="B122" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D122" s="44" t="s">
         <v>36</v>
@@ -68454,16 +69135,19 @@
       <c r="AG122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:33" ht="13">
+      <c r="AH122" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="123" spans="1:34" ht="13">
       <c r="A123" s="1" t="s">
-        <v>2088</v>
+        <v>2094</v>
       </c>
       <c r="B123" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D123" s="44" t="s">
         <v>36</v>
@@ -68555,16 +69239,19 @@
       <c r="AG123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:33" ht="13">
+      <c r="AH123" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="124" spans="1:34" ht="13">
       <c r="A124" s="1" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="B124" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D124" s="44" t="s">
         <v>36</v>
@@ -68656,16 +69343,19 @@
       <c r="AG124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:33" ht="13">
-      <c r="A125" s="1" t="s">
-        <v>2090</v>
+      <c r="AH124" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="125" spans="1:34" ht="14">
+      <c r="A125" s="61" t="s">
+        <v>2096</v>
       </c>
       <c r="B125" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D125" s="44" t="s">
         <v>36</v>
@@ -68757,16 +69447,19 @@
       <c r="AG125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:33" ht="13">
-      <c r="A126" s="1" t="s">
-        <v>2091</v>
+      <c r="AH125" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:34">
+      <c r="A126" s="44" t="s">
+        <v>1146</v>
       </c>
       <c r="B126" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D126" s="44" t="s">
         <v>36</v>
@@ -68858,16 +69551,19 @@
       <c r="AG126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:33" ht="13">
-      <c r="A127" s="1" t="s">
-        <v>2092</v>
+      <c r="AH126" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="127" spans="1:34">
+      <c r="A127" s="44" t="s">
+        <v>1143</v>
       </c>
       <c r="B127" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D127" s="44" t="s">
         <v>36</v>
@@ -68945,7 +69641,7 @@
         <v>11</v>
       </c>
       <c r="AC127" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="AD127" t="s">
         <v>36</v>
@@ -68959,16 +69655,19 @@
       <c r="AG127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:33" ht="13">
-      <c r="A128" s="1" t="s">
-        <v>2093</v>
+      <c r="AH127" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:34">
+      <c r="A128" s="44" t="s">
+        <v>1142</v>
       </c>
       <c r="B128" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C128">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D128" s="44" t="s">
         <v>36</v>
@@ -69046,7 +69745,7 @@
         <v>11</v>
       </c>
       <c r="AC128" t="s">
-        <v>1658</v>
+        <v>1665</v>
       </c>
       <c r="AD128" t="s">
         <v>36</v>
@@ -69060,16 +69759,19 @@
       <c r="AG128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:33" ht="13">
-      <c r="A129" s="1" t="s">
-        <v>2094</v>
+      <c r="AH128" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="129" spans="1:34">
+      <c r="A129" s="44" t="s">
+        <v>1740</v>
       </c>
       <c r="B129" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D129" s="44" t="s">
         <v>36</v>
@@ -69161,16 +69863,19 @@
       <c r="AG129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:33" ht="13">
-      <c r="A130" s="1" t="s">
-        <v>2095</v>
+      <c r="AH129" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="130" spans="1:34">
+      <c r="A130" s="44" t="s">
+        <v>959</v>
       </c>
       <c r="B130" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D130" s="44" t="s">
         <v>36</v>
@@ -69262,16 +69967,19 @@
       <c r="AG130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:33" ht="13">
-      <c r="A131" s="1" t="s">
-        <v>2096</v>
+      <c r="AH130" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131" spans="1:34">
+      <c r="A131" s="44" t="s">
+        <v>1719</v>
       </c>
       <c r="B131" s="44" t="s">
         <v>1368</v>
       </c>
       <c r="C131">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D131" s="44" t="s">
         <v>36</v>
@@ -69362,6 +70070,9 @@
       </c>
       <c r="AG131">
         <v>0</v>
+      </c>
+      <c r="AH131" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -69428,9 +70139,9 @@
     <col min="59" max="59" width="10" customWidth="1"/>
     <col min="60" max="60" width="11.54296875" customWidth="1"/>
     <col min="61" max="61" width="13.26953125" customWidth="1"/>
-    <col min="62" max="62" width="14.1796875" customWidth="1"/>
+    <col min="62" max="62" width="23.90625" customWidth="1"/>
     <col min="63" max="63" width="18.81640625" customWidth="1"/>
-    <col min="64" max="64" width="14.54296875" customWidth="1"/>
+    <col min="64" max="64" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="13">
@@ -69623,7 +70334,9 @@
       <c r="BK1" s="43" t="s">
         <v>2039</v>
       </c>
-      <c r="BL1" s="43"/>
+      <c r="BL1" s="43" t="s">
+        <v>2097</v>
+      </c>
     </row>
     <row r="2" spans="1:64">
       <c r="A2" s="44" t="s">
@@ -69815,6 +70528,9 @@
       <c r="BK2" t="s">
         <v>36</v>
       </c>
+      <c r="BL2" t="s">
+        <v>2098</v>
+      </c>
     </row>
     <row r="3" spans="1:64">
       <c r="A3" s="44" t="s">
@@ -70006,6 +70722,9 @@
       <c r="BK3" t="s">
         <v>36</v>
       </c>
+      <c r="BL3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="4" spans="1:64">
       <c r="A4" s="44" t="s">
@@ -70197,6 +70916,9 @@
       <c r="BK4" t="s">
         <v>36</v>
       </c>
+      <c r="BL4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="1:64">
       <c r="A5" s="44" t="s">
@@ -70388,6 +71110,9 @@
       <c r="BK5" t="s">
         <v>36</v>
       </c>
+      <c r="BL5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:64">
       <c r="A6" s="44" t="s">
@@ -70579,6 +71304,9 @@
       <c r="BK6" t="s">
         <v>36</v>
       </c>
+      <c r="BL6" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:64">
       <c r="A7" s="44" t="s">
@@ -70770,6 +71498,9 @@
       <c r="BK7" t="s">
         <v>36</v>
       </c>
+      <c r="BL7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:64">
       <c r="A8" s="44" t="s">
@@ -70961,6 +71692,9 @@
       <c r="BK8" t="s">
         <v>36</v>
       </c>
+      <c r="BL8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="9" spans="1:64">
       <c r="A9" s="44" t="s">
@@ -71152,6 +71886,9 @@
       <c r="BK9" t="s">
         <v>36</v>
       </c>
+      <c r="BL9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="10" spans="1:64">
       <c r="A10" s="44" t="s">
@@ -71343,6 +72080,9 @@
       <c r="BK10" t="s">
         <v>36</v>
       </c>
+      <c r="BL10" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:64">
       <c r="A11" s="44" t="s">
@@ -71534,6 +72274,9 @@
       <c r="BK11" t="s">
         <v>36</v>
       </c>
+      <c r="BL11" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="1:64">
       <c r="A12" s="44" t="s">
@@ -71725,6 +72468,9 @@
       <c r="BK12" t="s">
         <v>36</v>
       </c>
+      <c r="BL12" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:64">
       <c r="A13" s="44" t="s">
@@ -71916,6 +72662,9 @@
       <c r="BK13" t="s">
         <v>36</v>
       </c>
+      <c r="BL13" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="1:64">
       <c r="A14" s="44" t="s">
@@ -72107,6 +72856,9 @@
       <c r="BK14" t="s">
         <v>36</v>
       </c>
+      <c r="BL14" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" spans="1:64">
       <c r="A15" s="44" t="s">
@@ -72298,6 +73050,9 @@
       <c r="BK15" t="s">
         <v>36</v>
       </c>
+      <c r="BL15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="1:64">
       <c r="A16" s="44" t="s">
@@ -72489,8 +73244,11 @@
       <c r="BK16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:63">
+      <c r="BL16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:64">
       <c r="A17" s="44" t="s">
         <v>1911</v>
       </c>
@@ -72680,8 +73438,11 @@
       <c r="BK17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:63">
+      <c r="BL17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:64">
       <c r="A18" s="44" t="s">
         <v>1485</v>
       </c>
@@ -72871,8 +73632,11 @@
       <c r="BK18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:63">
+      <c r="BL18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:64">
       <c r="A19" s="44" t="s">
         <v>1489</v>
       </c>
@@ -73062,8 +73826,11 @@
       <c r="BK19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:63">
+      <c r="BL19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:64">
       <c r="A20" s="44" t="s">
         <v>1490</v>
       </c>
@@ -73253,8 +74020,11 @@
       <c r="BK20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:63">
+      <c r="BL20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:64">
       <c r="A21" s="44" t="s">
         <v>1914</v>
       </c>
@@ -73444,8 +74214,11 @@
       <c r="BK21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:63">
+      <c r="BL21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:64">
       <c r="A22" s="44" t="s">
         <v>1913</v>
       </c>
@@ -73635,8 +74408,11 @@
       <c r="BK22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="23" spans="1:63">
+      <c r="BL22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:64">
       <c r="A23" s="44" t="s">
         <v>1928</v>
       </c>
@@ -73826,8 +74602,11 @@
       <c r="BK23" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:63">
+      <c r="BL23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:64">
       <c r="A24" s="44" t="s">
         <v>1931</v>
       </c>
@@ -74017,8 +74796,11 @@
       <c r="BK24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:63">
+      <c r="BL24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:64">
       <c r="A25" s="44" t="s">
         <v>1929</v>
       </c>
@@ -74208,8 +74990,11 @@
       <c r="BK25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:63">
+      <c r="BL25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:64">
       <c r="A26" s="44" t="s">
         <v>1912</v>
       </c>
@@ -74399,8 +75184,11 @@
       <c r="BK26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:63">
+      <c r="BL26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:64">
       <c r="A27" s="44" t="s">
         <v>1494</v>
       </c>
@@ -74590,8 +75378,11 @@
       <c r="BK27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="1:63">
+      <c r="BL27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:64">
       <c r="A28" s="44" t="s">
         <v>1501</v>
       </c>
@@ -74781,8 +75572,11 @@
       <c r="BK28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:63">
+      <c r="BL28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:64">
       <c r="A29" s="44" t="s">
         <v>1502</v>
       </c>
@@ -74972,8 +75766,11 @@
       <c r="BK29" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="1:63">
+      <c r="BL29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:64">
       <c r="A30" s="44" t="s">
         <v>1431</v>
       </c>
@@ -75163,8 +75960,11 @@
       <c r="BK30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:63">
+      <c r="BL30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:64">
       <c r="A31" s="44" t="s">
         <v>1551</v>
       </c>
@@ -75354,8 +76154,11 @@
       <c r="BK31" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:63">
+      <c r="BL31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:64">
       <c r="A32" s="44" t="s">
         <v>1587</v>
       </c>
@@ -75545,8 +76348,11 @@
       <c r="BK32" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:63">
+      <c r="BL32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:64">
       <c r="A33" s="44" t="s">
         <v>935</v>
       </c>
@@ -75736,8 +76542,11 @@
       <c r="BK33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:63">
+      <c r="BL33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:64">
       <c r="A34" s="44" t="s">
         <v>1593</v>
       </c>
@@ -75927,8 +76736,11 @@
       <c r="BK34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:63">
+      <c r="BL34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:64">
       <c r="A35" s="44" t="s">
         <v>1602</v>
       </c>
@@ -76118,8 +76930,11 @@
       <c r="BK35" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="1:63">
+      <c r="BL35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:64">
       <c r="A36" s="44" t="s">
         <v>1611</v>
       </c>
@@ -76309,8 +77124,11 @@
       <c r="BK36" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:63">
+      <c r="BL36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:64">
       <c r="A37" s="44" t="s">
         <v>1615</v>
       </c>
@@ -76500,8 +77318,11 @@
       <c r="BK37" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:63">
+      <c r="BL37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:64">
       <c r="A38" s="44" t="s">
         <v>1616</v>
       </c>
@@ -76691,8 +77512,11 @@
       <c r="BK38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:63">
+      <c r="BL38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:64">
       <c r="A39" s="44" t="s">
         <v>1620</v>
       </c>
@@ -76882,8 +77706,11 @@
       <c r="BK39" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:63">
+      <c r="BL39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:64">
       <c r="A40" s="44" t="s">
         <v>1624</v>
       </c>
@@ -77073,8 +77900,11 @@
       <c r="BK40" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:63">
+      <c r="BL40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:64">
       <c r="A41" s="44" t="s">
         <v>1647</v>
       </c>
@@ -77264,8 +78094,11 @@
       <c r="BK41" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="42" spans="1:63">
+      <c r="BL41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:64">
       <c r="A42" s="44" t="s">
         <v>1578</v>
       </c>
@@ -77455,8 +78288,11 @@
       <c r="BK42" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:63">
+      <c r="BL42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:64">
       <c r="A43" s="44" t="s">
         <v>1686</v>
       </c>
@@ -77646,8 +78482,11 @@
       <c r="BK43" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="44" spans="1:63">
+      <c r="BL43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:64">
       <c r="A44" s="44" t="s">
         <v>1728</v>
       </c>
@@ -77837,8 +78676,11 @@
       <c r="BK44" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="45" spans="1:63">
+      <c r="BL44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:64">
       <c r="A45" s="44" t="s">
         <v>1786</v>
       </c>
@@ -78028,8 +78870,11 @@
       <c r="BK45" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="46" spans="1:63">
+      <c r="BL45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:64">
       <c r="A46" s="44" t="s">
         <v>1904</v>
       </c>
@@ -78219,8 +79064,11 @@
       <c r="BK46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="47" spans="1:63">
+      <c r="BL46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:64">
       <c r="A47" s="44" t="s">
         <v>1905</v>
       </c>
@@ -78410,8 +79258,11 @@
       <c r="BK47" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="48" spans="1:63">
+      <c r="BL47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:64">
       <c r="A48" s="44" t="s">
         <v>1906</v>
       </c>
@@ -78601,8 +79452,11 @@
       <c r="BK48" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="49" spans="1:63">
+      <c r="BL48" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:64">
       <c r="A49" s="44" t="s">
         <v>1923</v>
       </c>
@@ -78792,8 +79646,11 @@
       <c r="BK49" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="1:63">
+      <c r="BL49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:64">
       <c r="A50" s="44" t="s">
         <v>1924</v>
       </c>
@@ -78983,8 +79840,11 @@
       <c r="BK50" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="51" spans="1:63">
+      <c r="BL50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:64">
       <c r="A51" s="44" t="s">
         <v>2040</v>
       </c>
@@ -79174,8 +80034,11 @@
       <c r="BK51" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="52" spans="1:63">
+      <c r="BL51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:64">
       <c r="A52" s="44" t="s">
         <v>2041</v>
       </c>
@@ -79365,8 +80228,11 @@
       <c r="BK52" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="53" spans="1:63">
+      <c r="BL52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:64">
       <c r="A53" s="44" t="s">
         <v>2052</v>
       </c>
@@ -79556,8 +80422,11 @@
       <c r="BK53" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="54" spans="1:63">
+      <c r="BL53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:64">
       <c r="A54" s="44" t="s">
         <v>2053</v>
       </c>
@@ -79747,8 +80616,11 @@
       <c r="BK54" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="55" spans="1:63">
+      <c r="BL54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:64">
       <c r="A55" s="44" t="s">
         <v>1797</v>
       </c>
@@ -79938,8 +80810,11 @@
       <c r="BK55" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="56" spans="1:63">
+      <c r="BL55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:64">
       <c r="A56" s="44" t="s">
         <v>1796</v>
       </c>
@@ -80129,8 +81004,11 @@
       <c r="BK56" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="57" spans="1:63">
+      <c r="BL56" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:64">
       <c r="A57" s="44" t="s">
         <v>1805</v>
       </c>
@@ -80320,8 +81198,11 @@
       <c r="BK57" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="58" spans="1:63">
+      <c r="BL57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:64">
       <c r="A58" s="44" t="s">
         <v>1807</v>
       </c>
@@ -80511,8 +81392,11 @@
       <c r="BK58" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="59" spans="1:63">
+      <c r="BL58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:64">
       <c r="A59" s="44" t="s">
         <v>1934</v>
       </c>
@@ -80702,8 +81586,11 @@
       <c r="BK59" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="60" spans="1:63">
+      <c r="BL59" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:64">
       <c r="A60" s="44" t="s">
         <v>1935</v>
       </c>
@@ -80893,8 +81780,11 @@
       <c r="BK60" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="61" spans="1:63">
+      <c r="BL60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:64">
       <c r="A61" s="44" t="s">
         <v>1868</v>
       </c>
@@ -81084,8 +81974,11 @@
       <c r="BK61" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="62" spans="1:63">
+      <c r="BL61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:64">
       <c r="A62" s="44" t="s">
         <v>1869</v>
       </c>
@@ -81275,8 +82168,11 @@
       <c r="BK62" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="63" spans="1:63">
+      <c r="BL62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:64">
       <c r="A63" s="44" t="s">
         <v>1925</v>
       </c>
@@ -81466,8 +82362,11 @@
       <c r="BK63" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="64" spans="1:63">
+      <c r="BL63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:64">
       <c r="A64" s="44" t="s">
         <v>1926</v>
       </c>
@@ -81657,8 +82556,11 @@
       <c r="BK64" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="65" spans="1:63">
+      <c r="BL64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:64">
       <c r="A65" s="44" t="s">
         <v>1870</v>
       </c>
@@ -81848,8 +82750,11 @@
       <c r="BK65" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="66" spans="1:63">
+      <c r="BL65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:64">
       <c r="A66" s="44" t="s">
         <v>1871</v>
       </c>
@@ -82039,8 +82944,11 @@
       <c r="BK66" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="67" spans="1:63">
+      <c r="BL66" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:64">
       <c r="A67" s="44" t="s">
         <v>1882</v>
       </c>
@@ -82230,8 +83138,11 @@
       <c r="BK67" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="68" spans="1:63">
+      <c r="BL67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:64">
       <c r="A68" s="44" t="s">
         <v>1883</v>
       </c>
@@ -82421,8 +83332,11 @@
       <c r="BK68" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="69" spans="1:63">
+      <c r="BL68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:64">
       <c r="A69" s="44" t="s">
         <v>1908</v>
       </c>
@@ -82612,8 +83526,11 @@
       <c r="BK69" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="70" spans="1:63">
+      <c r="BL69" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:64">
       <c r="A70" s="44" t="s">
         <v>1907</v>
       </c>
@@ -82803,8 +83720,11 @@
       <c r="BK70" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="71" spans="1:63">
+      <c r="BL70" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:64">
       <c r="A71" s="44" t="s">
         <v>1884</v>
       </c>
@@ -82994,8 +83914,11 @@
       <c r="BK71" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="72" spans="1:63">
+      <c r="BL71" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:64">
       <c r="A72" s="44" t="s">
         <v>1938</v>
       </c>
@@ -83185,8 +84108,11 @@
       <c r="BK72" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="73" spans="1:63">
+      <c r="BL72" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:64">
       <c r="A73" s="44" t="s">
         <v>1940</v>
       </c>
@@ -83376,8 +84302,11 @@
       <c r="BK73" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="74" spans="1:63" ht="14">
+      <c r="BL73" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:64" ht="14">
       <c r="A74" s="55" t="s">
         <v>1886</v>
       </c>
@@ -83409,8 +84338,11 @@
       <c r="BJ74" s="46" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="75" spans="1:63">
+      <c r="BL74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:64">
       <c r="A75" s="44" t="s">
         <v>1887</v>
       </c>
@@ -83600,8 +84532,11 @@
       <c r="BK75" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="76" spans="1:63">
+      <c r="BL75" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:64">
       <c r="A76" s="44" t="s">
         <v>1888</v>
       </c>
@@ -83791,8 +84726,11 @@
       <c r="BK76" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="77" spans="1:63">
+      <c r="BL76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:64">
       <c r="A77" s="44" t="s">
         <v>1897</v>
       </c>
@@ -83982,8 +84920,11 @@
       <c r="BK77" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="78" spans="1:63">
+      <c r="BL77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:64">
       <c r="A78" s="44" t="s">
         <v>1901</v>
       </c>
@@ -84173,8 +85114,11 @@
       <c r="BK78" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="79" spans="1:63">
+      <c r="BL78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="1:64">
       <c r="A79" s="44" t="s">
         <v>1943</v>
       </c>
@@ -84364,8 +85308,11 @@
       <c r="BK79" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="80" spans="1:63">
+      <c r="BL79" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:64">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
